--- a/_downloads/6389148f3813c4a2cb904a2a4100c2de/data_query_matrix.xlsx
+++ b/_downloads/6389148f3813c4a2cb904a2a4100c2de/data_query_matrix.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR6"/>
+  <dimension ref="A1:AU6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -434,42 +434,45 @@
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="50" customWidth="1" min="9" max="9"/>
-    <col width="37" customWidth="1" min="10" max="10"/>
-    <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="50" customWidth="1" min="12" max="12"/>
-    <col width="29" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="24" customWidth="1" min="15" max="15"/>
-    <col width="50" customWidth="1" min="16" max="16"/>
-    <col width="8" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="22" customWidth="1" min="19" max="19"/>
-    <col width="19" customWidth="1" min="20" max="20"/>
-    <col width="18" customWidth="1" min="21" max="21"/>
-    <col width="24" customWidth="1" min="22" max="22"/>
-    <col width="50" customWidth="1" min="23" max="23"/>
-    <col width="45" customWidth="1" min="24" max="24"/>
-    <col width="10" customWidth="1" min="25" max="25"/>
-    <col width="13" customWidth="1" min="26" max="26"/>
-    <col width="16" customWidth="1" min="27" max="27"/>
+    <col width="37" customWidth="1" min="13" max="13"/>
+    <col width="50" customWidth="1" min="14" max="14"/>
+    <col width="50" customWidth="1" min="15" max="15"/>
+    <col width="29" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="50" customWidth="1" min="19" max="19"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="22" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="24" max="24"/>
+    <col width="24" customWidth="1" min="25" max="25"/>
+    <col width="50" customWidth="1" min="26" max="26"/>
+    <col width="45" customWidth="1" min="27" max="27"/>
     <col width="10" customWidth="1" min="28" max="28"/>
-    <col width="11" customWidth="1" min="29" max="29"/>
-    <col width="11" customWidth="1" min="30" max="30"/>
-    <col width="13" customWidth="1" min="31" max="31"/>
+    <col width="13" customWidth="1" min="29" max="29"/>
+    <col width="16" customWidth="1" min="30" max="30"/>
+    <col width="10" customWidth="1" min="31" max="31"/>
     <col width="11" customWidth="1" min="32" max="32"/>
     <col width="11" customWidth="1" min="33" max="33"/>
-    <col width="11" customWidth="1" min="34" max="34"/>
-    <col width="12" customWidth="1" min="35" max="35"/>
-    <col width="8" customWidth="1" min="36" max="36"/>
-    <col width="7" customWidth="1" min="37" max="37"/>
-    <col width="8" customWidth="1" min="38" max="38"/>
+    <col width="13" customWidth="1" min="34" max="34"/>
+    <col width="11" customWidth="1" min="35" max="35"/>
+    <col width="11" customWidth="1" min="36" max="36"/>
+    <col width="11" customWidth="1" min="37" max="37"/>
+    <col width="12" customWidth="1" min="38" max="38"/>
     <col width="8" customWidth="1" min="39" max="39"/>
-    <col width="41" customWidth="1" min="40" max="40"/>
-    <col width="46" customWidth="1" min="41" max="41"/>
-    <col width="50" customWidth="1" min="42" max="42"/>
-    <col width="38" customWidth="1" min="43" max="43"/>
-    <col width="50" customWidth="1" min="44" max="44"/>
+    <col width="7" customWidth="1" min="40" max="40"/>
+    <col width="8" customWidth="1" min="41" max="41"/>
+    <col width="8" customWidth="1" min="42" max="42"/>
+    <col width="41" customWidth="1" min="43" max="43"/>
+    <col width="46" customWidth="1" min="44" max="44"/>
+    <col width="50" customWidth="1" min="45" max="45"/>
+    <col width="38" customWidth="1" min="46" max="46"/>
+    <col width="50" customWidth="1" min="47" max="47"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -515,180 +518,195 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>LogicalAnd</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>LogicalOr</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>LogicalXor</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>ProcedureDefinition</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>FunctionDefinition</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>IfElse</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>SwitchCase</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Loop</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ForLoop</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>TryCatch</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Raise</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Thread</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>SendMessage</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>ReceiveMessage</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>SingleLineComment</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>MultiLineComment</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Print</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Import</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Constant</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Addition</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Subtraction</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Multiplication</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Division</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Remainder</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Floor</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Rounding</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Increment</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Decrement</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>LeftShift</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>RightShift</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>BitAnd</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>BitOr</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>BitXor</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>BitNot</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Float4VectorMultiplication</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>Float4VectorDotProduct</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>Float4VectorCrossProduct</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>SetFiltering</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>SetJoin</t>
         </is>
@@ -1899,6 +1917,21 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -2070,7 +2103,7 @@
           </r>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2323,7 +2356,7 @@
           </r>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2510,7 +2543,7 @@
           </r>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2694,7 +2727,7 @@
           </r>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2875,7 +2908,7 @@
           </r>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="Q2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3154,7 +3187,7 @@
           </r>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
+      <c r="R2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3326,7 +3359,7 @@
           </r>
         </is>
       </c>
-      <c r="P2" s="3" t="inlineStr">
+      <c r="S2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3400,22 +3433,22 @@
           </r>
         </is>
       </c>
-      <c r="Q2" s="3" t="inlineStr">
+      <c r="T2" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="R2" s="3" t="inlineStr">
+      <c r="U2" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S2" s="3" t="inlineStr">
+      <c r="V2" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="T2" s="3" t="inlineStr">
+      <c r="W2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3427,7 +3460,7 @@
           </r>
         </is>
       </c>
-      <c r="U2" s="3" t="inlineStr">
+      <c r="X2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3460,7 +3493,7 @@
           </r>
         </is>
       </c>
-      <c r="V2" s="3" t="inlineStr">
+      <c r="Y2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3496,12 +3529,12 @@
           </r>
         </is>
       </c>
-      <c r="W2" s="3" t="inlineStr">
+      <c r="Z2" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="X2" s="3" t="inlineStr">
+      <c r="AA2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3584,7 +3617,7 @@
           </r>
         </is>
       </c>
-      <c r="Y2" s="3" t="inlineStr">
+      <c r="AB2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3626,7 +3659,7 @@
           </r>
         </is>
       </c>
-      <c r="Z2" s="3" t="inlineStr">
+      <c r="AC2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3668,7 +3701,7 @@
           </r>
         </is>
       </c>
-      <c r="AA2" s="3" t="inlineStr">
+      <c r="AD2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3710,7 +3743,7 @@
           </r>
         </is>
       </c>
-      <c r="AB2" s="3" t="inlineStr">
+      <c r="AE2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3752,7 +3785,7 @@
           </r>
         </is>
       </c>
-      <c r="AC2" s="3" t="inlineStr">
+      <c r="AF2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3794,7 +3827,7 @@
           </r>
         </is>
       </c>
-      <c r="AD2" s="3" t="inlineStr">
+      <c r="AG2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3829,7 +3862,7 @@
           </r>
         </is>
       </c>
-      <c r="AE2" s="3" t="inlineStr">
+      <c r="AH2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3883,7 +3916,7 @@
           </r>
         </is>
       </c>
-      <c r="AF2" s="3" t="inlineStr">
+      <c r="AI2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3926,7 +3959,7 @@
           </r>
         </is>
       </c>
-      <c r="AG2" s="3" t="inlineStr">
+      <c r="AJ2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3969,17 +4002,17 @@
           </r>
         </is>
       </c>
-      <c r="AH2" s="3" t="inlineStr">
+      <c r="AK2" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AI2" s="3" t="inlineStr">
+      <c r="AL2" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AJ2" s="3" t="inlineStr">
+      <c r="AM2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4021,7 +4054,7 @@
           </r>
         </is>
       </c>
-      <c r="AK2" s="3" t="inlineStr">
+      <c r="AN2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4063,7 +4096,7 @@
           </r>
         </is>
       </c>
-      <c r="AL2" s="3" t="inlineStr">
+      <c r="AO2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4105,7 +4138,7 @@
           </r>
         </is>
       </c>
-      <c r="AM2" s="3" t="inlineStr">
+      <c r="AP2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4129,7 +4162,7 @@
           </r>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
+      <c r="AQ2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4265,7 +4298,7 @@
           </r>
         </is>
       </c>
-      <c r="AO2" s="3" t="inlineStr">
+      <c r="AR2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4422,7 +4455,7 @@
           </r>
         </is>
       </c>
-      <c r="AP2" s="3" t="inlineStr">
+      <c r="AS2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4673,7 +4706,7 @@
           </r>
         </is>
       </c>
-      <c r="AQ2" s="3" t="inlineStr">
+      <c r="AT2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4761,7 +4794,7 @@
           </r>
         </is>
       </c>
-      <c r="AR2" s="3" t="inlineStr">
+      <c r="AU2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5534,6 +5567,21 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -5767,7 +5815,7 @@
           </r>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6037,7 +6085,7 @@
           </r>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6164,7 +6212,7 @@
           </r>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6357,7 +6405,7 @@
           </r>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6484,7 +6532,7 @@
           </r>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="Q3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6606,7 +6654,7 @@
           </r>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="R3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6764,7 +6812,7 @@
           </r>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr">
+      <c r="S3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6858,22 +6906,22 @@
           </r>
         </is>
       </c>
-      <c r="Q3" s="3" t="inlineStr">
+      <c r="T3" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="R3" s="3" t="inlineStr">
+      <c r="U3" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S3" s="3" t="inlineStr">
+      <c r="V3" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="T3" s="3" t="inlineStr">
+      <c r="W3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6905,7 +6953,7 @@
           </r>
         </is>
       </c>
-      <c r="U3" s="3" t="inlineStr">
+      <c r="X3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6938,7 +6986,7 @@
           </r>
         </is>
       </c>
-      <c r="V3" s="3" t="inlineStr">
+      <c r="Y3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6956,7 +7004,7 @@
           </r>
         </is>
       </c>
-      <c r="W3" s="3" t="inlineStr">
+      <c r="Z3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7045,7 +7093,7 @@
           </r>
         </is>
       </c>
-      <c r="X3" s="3" t="inlineStr">
+      <c r="AA3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7153,7 +7201,7 @@
           </r>
         </is>
       </c>
-      <c r="Y3" s="3" t="inlineStr">
+      <c r="AB3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7195,7 +7243,7 @@
           </r>
         </is>
       </c>
-      <c r="Z3" s="3" t="inlineStr">
+      <c r="AC3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7237,7 +7285,7 @@
           </r>
         </is>
       </c>
-      <c r="AA3" s="3" t="inlineStr">
+      <c r="AD3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7279,7 +7327,7 @@
           </r>
         </is>
       </c>
-      <c r="AB3" s="3" t="inlineStr">
+      <c r="AE3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7321,7 +7369,7 @@
           </r>
         </is>
       </c>
-      <c r="AC3" s="3" t="inlineStr">
+      <c r="AF3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7363,7 +7411,7 @@
           </r>
         </is>
       </c>
-      <c r="AD3" s="3" t="inlineStr">
+      <c r="AG3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7399,7 +7447,7 @@
           </r>
         </is>
       </c>
-      <c r="AE3" s="3" t="inlineStr">
+      <c r="AH3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7435,7 +7483,7 @@
           </r>
         </is>
       </c>
-      <c r="AF3" s="3" t="inlineStr">
+      <c r="AI3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7478,7 +7526,7 @@
           </r>
         </is>
       </c>
-      <c r="AG3" s="3" t="inlineStr">
+      <c r="AJ3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7521,37 +7569,37 @@
           </r>
         </is>
       </c>
-      <c r="AH3" s="3" t="inlineStr">
+      <c r="AK3" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AI3" s="3" t="inlineStr">
+      <c r="AL3" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AJ3" s="3" t="inlineStr">
+      <c r="AM3" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AK3" s="3" t="inlineStr">
+      <c r="AN3" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AL3" s="3" t="inlineStr">
+      <c r="AO3" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AM3" s="3" t="inlineStr">
+      <c r="AP3" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
+      <c r="AQ3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7754,7 +7802,7 @@
           </r>
         </is>
       </c>
-      <c r="AO3" s="3" t="inlineStr">
+      <c r="AR3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7976,7 +8024,7 @@
           </r>
         </is>
       </c>
-      <c r="AP3" s="3" t="inlineStr">
+      <c r="AS3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8525,7 +8573,7 @@
           </r>
         </is>
       </c>
-      <c r="AQ3" s="3" t="inlineStr">
+      <c r="AT3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8672,7 +8720,7 @@
           </r>
         </is>
       </c>
-      <c r="AR3" s="3" t="inlineStr">
+      <c r="AU3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9252,6 +9300,21 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -9432,7 +9495,7 @@
           </r>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9737,42 +9800,42 @@
           </r>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="P4" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="Q4" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="R4" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr">
+      <c r="S4" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="inlineStr">
+      <c r="T4" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="R4" s="3" t="inlineStr">
+      <c r="U4" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S4" s="3" t="inlineStr">
+      <c r="V4" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9826,7 +9889,7 @@
           </r>
         </is>
       </c>
-      <c r="T4" s="3" t="inlineStr">
+      <c r="W4" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9844,7 +9907,7 @@
           </r>
         </is>
       </c>
-      <c r="U4" s="3" t="inlineStr">
+      <c r="X4" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9945,112 +10008,112 @@
           </r>
         </is>
       </c>
-      <c r="V4" s="3" t="inlineStr">
+      <c r="Y4" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="W4" s="3" t="inlineStr">
+      <c r="Z4" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="X4" s="3" t="inlineStr">
+      <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
+      <c r="AB4" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="Z4" s="3" t="inlineStr">
+      <c r="AC4" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AA4" s="3" t="inlineStr">
+      <c r="AD4" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AB4" s="3" t="inlineStr">
+      <c r="AE4" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AC4" s="3" t="inlineStr">
+      <c r="AF4" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AD4" s="3" t="inlineStr">
+      <c r="AG4" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AE4" s="3" t="inlineStr">
+      <c r="AH4" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AF4" s="3" t="inlineStr">
+      <c r="AI4" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AG4" s="3" t="inlineStr">
+      <c r="AJ4" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AH4" s="3" t="inlineStr">
+      <c r="AK4" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AI4" s="3" t="inlineStr">
+      <c r="AL4" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AJ4" s="3" t="inlineStr">
+      <c r="AM4" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AK4" s="3" t="inlineStr">
+      <c r="AN4" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AL4" s="3" t="inlineStr">
+      <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AM4" s="3" t="inlineStr">
+      <c r="AP4" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
+      <c r="AQ4" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AO4" s="3" t="inlineStr">
+      <c r="AR4" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AP4" s="3" t="inlineStr">
+      <c r="AS4" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AQ4" s="3" t="inlineStr">
+      <c r="AT4" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10133,7 +10196,7 @@
           </r>
         </is>
       </c>
-      <c r="AR4" s="3" t="inlineStr">
+      <c r="AU4" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10615,6 +10678,21 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -10759,7 +10837,7 @@
           </r>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11046,42 +11124,42 @@
           </r>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="Q5" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="R5" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr">
+      <c r="S5" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="Q5" s="3" t="inlineStr">
+      <c r="T5" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="R5" s="3" t="inlineStr">
+      <c r="U5" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S5" s="3" t="inlineStr">
+      <c r="V5" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="T5" s="3" t="inlineStr">
+      <c r="W5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11099,17 +11177,17 @@
           </r>
         </is>
       </c>
-      <c r="U5" s="3" t="inlineStr">
+      <c r="X5" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="V5" s="3" t="inlineStr">
+      <c r="Y5" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="W5" s="3" t="inlineStr">
+      <c r="Z5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11158,7 +11236,7 @@
           </r>
         </is>
       </c>
-      <c r="X5" s="3" t="inlineStr">
+      <c r="AA5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11226,7 +11304,7 @@
           </r>
         </is>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
+      <c r="AB5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11270,7 +11348,7 @@
           </r>
         </is>
       </c>
-      <c r="Z5" s="3" t="inlineStr">
+      <c r="AC5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11314,7 +11392,7 @@
           </r>
         </is>
       </c>
-      <c r="AA5" s="3" t="inlineStr">
+      <c r="AD5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11358,7 +11436,7 @@
           </r>
         </is>
       </c>
-      <c r="AB5" s="3" t="inlineStr">
+      <c r="AE5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11402,12 +11480,12 @@
           </r>
         </is>
       </c>
-      <c r="AC5" s="3" t="inlineStr">
+      <c r="AF5" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AD5" s="3" t="inlineStr">
+      <c r="AG5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11444,7 +11522,7 @@
           </r>
         </is>
       </c>
-      <c r="AE5" s="3" t="inlineStr">
+      <c r="AH5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11481,7 +11559,7 @@
           </r>
         </is>
       </c>
-      <c r="AF5" s="3" t="inlineStr">
+      <c r="AI5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11525,7 +11603,7 @@
           </r>
         </is>
       </c>
-      <c r="AG5" s="3" t="inlineStr">
+      <c r="AJ5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11569,52 +11647,52 @@
           </r>
         </is>
       </c>
-      <c r="AH5" s="3" t="inlineStr">
+      <c r="AK5" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AI5" s="3" t="inlineStr">
+      <c r="AL5" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AJ5" s="3" t="inlineStr">
+      <c r="AM5" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AK5" s="3" t="inlineStr">
+      <c r="AN5" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AL5" s="3" t="inlineStr">
+      <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AM5" s="3" t="inlineStr">
+      <c r="AP5" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
+      <c r="AQ5" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AO5" s="3" t="inlineStr">
+      <c r="AR5" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AP5" s="3" t="inlineStr">
+      <c r="AS5" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AQ5" s="3" t="inlineStr">
+      <c r="AT5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11677,7 +11755,7 @@
           </r>
         </is>
       </c>
-      <c r="AR5" s="3" t="inlineStr">
+      <c r="AU5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11856,6 +11934,21 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -11865,12 +11958,12 @@
           </r>
         </is>
       </c>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="O6" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="P6" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11881,7 +11974,7 @@
           </r>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
+      <c r="Q6" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11892,32 +11985,32 @@
           </r>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
+      <c r="R6" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="P6" s="3" t="inlineStr">
+      <c r="S6" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="Q6" s="3" t="inlineStr">
+      <c r="T6" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="R6" s="3" t="inlineStr">
+      <c r="U6" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S6" s="3" t="inlineStr">
+      <c r="V6" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="T6" s="3" t="inlineStr">
+      <c r="W6" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11928,7 +12021,7 @@
           </r>
         </is>
       </c>
-      <c r="U6" s="3" t="inlineStr">
+      <c r="X6" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11939,7 +12032,7 @@
           </r>
         </is>
       </c>
-      <c r="V6" s="3" t="inlineStr">
+      <c r="Y6" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11950,7 +12043,7 @@
           </r>
         </is>
       </c>
-      <c r="W6" s="3" t="inlineStr">
+      <c r="Z6" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11961,7 +12054,7 @@
           </r>
         </is>
       </c>
-      <c r="X6" s="3" t="inlineStr">
+      <c r="AA6" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11972,97 +12065,97 @@
           </r>
         </is>
       </c>
-      <c r="Y6" s="3" t="inlineStr">
+      <c r="AB6" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="Z6" s="3" t="inlineStr">
+      <c r="AC6" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AA6" s="3" t="inlineStr">
+      <c r="AD6" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AB6" s="3" t="inlineStr">
+      <c r="AE6" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AC6" s="3" t="inlineStr">
+      <c r="AF6" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AD6" s="3" t="inlineStr">
+      <c r="AG6" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AE6" s="3" t="inlineStr">
+      <c r="AH6" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AF6" s="3" t="inlineStr">
+      <c r="AI6" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AG6" s="3" t="inlineStr">
+      <c r="AJ6" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AH6" s="3" t="inlineStr">
+      <c r="AK6" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AI6" s="3" t="inlineStr">
+      <c r="AL6" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AJ6" s="3" t="inlineStr">
+      <c r="AM6" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AK6" s="3" t="inlineStr">
+      <c r="AN6" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AL6" s="3" t="inlineStr">
+      <c r="AO6" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AM6" s="3" t="inlineStr">
+      <c r="AP6" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
+      <c r="AQ6" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AO6" s="3" t="inlineStr">
+      <c r="AR6" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AP6" s="3" t="inlineStr">
+      <c r="AS6" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AQ6" s="3" t="inlineStr">
+      <c r="AT6" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12073,7 +12166,7 @@
           </r>
         </is>
       </c>
-      <c r="AR6" s="3" t="inlineStr">
+      <c r="AU6" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>

--- a/_downloads/6389148f3813c4a2cb904a2a4100c2de/data_query_matrix.xlsx
+++ b/_downloads/6389148f3813c4a2cb904a2a4100c2de/data_query_matrix.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU6"/>
+  <dimension ref="A1:BA6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -448,31 +448,37 @@
     <col width="8" customWidth="1" min="20" max="20"/>
     <col width="13" customWidth="1" min="21" max="21"/>
     <col width="22" customWidth="1" min="22" max="22"/>
-    <col width="19" customWidth="1" min="23" max="23"/>
-    <col width="18" customWidth="1" min="24" max="24"/>
-    <col width="24" customWidth="1" min="25" max="25"/>
-    <col width="50" customWidth="1" min="26" max="26"/>
-    <col width="45" customWidth="1" min="27" max="27"/>
-    <col width="10" customWidth="1" min="28" max="28"/>
-    <col width="13" customWidth="1" min="29" max="29"/>
-    <col width="16" customWidth="1" min="30" max="30"/>
-    <col width="10" customWidth="1" min="31" max="31"/>
-    <col width="11" customWidth="1" min="32" max="32"/>
-    <col width="11" customWidth="1" min="33" max="33"/>
-    <col width="13" customWidth="1" min="34" max="34"/>
-    <col width="11" customWidth="1" min="35" max="35"/>
-    <col width="11" customWidth="1" min="36" max="36"/>
-    <col width="11" customWidth="1" min="37" max="37"/>
-    <col width="12" customWidth="1" min="38" max="38"/>
-    <col width="8" customWidth="1" min="39" max="39"/>
-    <col width="7" customWidth="1" min="40" max="40"/>
-    <col width="8" customWidth="1" min="41" max="41"/>
-    <col width="8" customWidth="1" min="42" max="42"/>
-    <col width="41" customWidth="1" min="43" max="43"/>
-    <col width="46" customWidth="1" min="44" max="44"/>
-    <col width="50" customWidth="1" min="45" max="45"/>
-    <col width="38" customWidth="1" min="46" max="46"/>
-    <col width="50" customWidth="1" min="47" max="47"/>
+    <col width="17" customWidth="1" min="23" max="23"/>
+    <col width="11" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="21" customWidth="1" min="26" max="26"/>
+    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="17" customWidth="1" min="28" max="28"/>
+    <col width="19" customWidth="1" min="29" max="29"/>
+    <col width="18" customWidth="1" min="30" max="30"/>
+    <col width="24" customWidth="1" min="31" max="31"/>
+    <col width="50" customWidth="1" min="32" max="32"/>
+    <col width="45" customWidth="1" min="33" max="33"/>
+    <col width="10" customWidth="1" min="34" max="34"/>
+    <col width="13" customWidth="1" min="35" max="35"/>
+    <col width="16" customWidth="1" min="36" max="36"/>
+    <col width="10" customWidth="1" min="37" max="37"/>
+    <col width="11" customWidth="1" min="38" max="38"/>
+    <col width="11" customWidth="1" min="39" max="39"/>
+    <col width="13" customWidth="1" min="40" max="40"/>
+    <col width="11" customWidth="1" min="41" max="41"/>
+    <col width="11" customWidth="1" min="42" max="42"/>
+    <col width="11" customWidth="1" min="43" max="43"/>
+    <col width="12" customWidth="1" min="44" max="44"/>
+    <col width="8" customWidth="1" min="45" max="45"/>
+    <col width="7" customWidth="1" min="46" max="46"/>
+    <col width="8" customWidth="1" min="47" max="47"/>
+    <col width="8" customWidth="1" min="48" max="48"/>
+    <col width="41" customWidth="1" min="49" max="49"/>
+    <col width="46" customWidth="1" min="50" max="50"/>
+    <col width="50" customWidth="1" min="51" max="51"/>
+    <col width="38" customWidth="1" min="52" max="52"/>
+    <col width="50" customWidth="1" min="53" max="53"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -588,125 +594,155 @@
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
+          <t>MutexDefinition</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>MutexLock</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>MutexUnlock</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>SemaphoreDefinition</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>SemaphoreWait</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>SemaphoreSignal</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>SingleLineComment</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>MultiLineComment</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Print</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Import</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Constant</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Addition</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Subtraction</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Multiplication</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Division</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Remainder</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Floor</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Rounding</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Increment</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Decrement</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>LeftShift</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>RightShift</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>BitAnd</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>BitOr</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>BitXor</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>BitNot</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>Float4VectorMultiplication</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>Float4VectorDotProduct</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>Float4VectorCrossProduct</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>SetFiltering</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>SetJoin</t>
         </is>
@@ -3450,6 +3486,36 @@
       </c>
       <c r="W2" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X2" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Y2" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Z2" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AA2" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AB2" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AC2" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -3460,7 +3526,7 @@
           </r>
         </is>
       </c>
-      <c r="X2" s="3" t="inlineStr">
+      <c r="AD2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3493,7 +3559,7 @@
           </r>
         </is>
       </c>
-      <c r="Y2" s="3" t="inlineStr">
+      <c r="AE2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3529,12 +3595,12 @@
           </r>
         </is>
       </c>
-      <c r="Z2" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AA2" s="3" t="inlineStr">
+      <c r="AF2" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AG2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3617,7 +3683,7 @@
           </r>
         </is>
       </c>
-      <c r="AB2" s="3" t="inlineStr">
+      <c r="AH2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3659,7 +3725,7 @@
           </r>
         </is>
       </c>
-      <c r="AC2" s="3" t="inlineStr">
+      <c r="AI2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3701,7 +3767,7 @@
           </r>
         </is>
       </c>
-      <c r="AD2" s="3" t="inlineStr">
+      <c r="AJ2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3743,7 +3809,7 @@
           </r>
         </is>
       </c>
-      <c r="AE2" s="3" t="inlineStr">
+      <c r="AK2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3785,7 +3851,7 @@
           </r>
         </is>
       </c>
-      <c r="AF2" s="3" t="inlineStr">
+      <c r="AL2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3827,7 +3893,7 @@
           </r>
         </is>
       </c>
-      <c r="AG2" s="3" t="inlineStr">
+      <c r="AM2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3862,7 +3928,7 @@
           </r>
         </is>
       </c>
-      <c r="AH2" s="3" t="inlineStr">
+      <c r="AN2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3916,7 +3982,7 @@
           </r>
         </is>
       </c>
-      <c r="AI2" s="3" t="inlineStr">
+      <c r="AO2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3959,7 +4025,7 @@
           </r>
         </is>
       </c>
-      <c r="AJ2" s="3" t="inlineStr">
+      <c r="AP2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4002,17 +4068,17 @@
           </r>
         </is>
       </c>
-      <c r="AK2" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AL2" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AM2" s="3" t="inlineStr">
+      <c r="AQ2" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AR2" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AS2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4054,7 +4120,7 @@
           </r>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
+      <c r="AT2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4096,7 +4162,7 @@
           </r>
         </is>
       </c>
-      <c r="AO2" s="3" t="inlineStr">
+      <c r="AU2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4138,7 +4204,7 @@
           </r>
         </is>
       </c>
-      <c r="AP2" s="3" t="inlineStr">
+      <c r="AV2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4162,7 +4228,7 @@
           </r>
         </is>
       </c>
-      <c r="AQ2" s="3" t="inlineStr">
+      <c r="AW2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4298,7 +4364,7 @@
           </r>
         </is>
       </c>
-      <c r="AR2" s="3" t="inlineStr">
+      <c r="AX2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4455,7 +4521,7 @@
           </r>
         </is>
       </c>
-      <c r="AS2" s="3" t="inlineStr">
+      <c r="AY2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4706,7 +4772,7 @@
           </r>
         </is>
       </c>
-      <c r="AT2" s="3" t="inlineStr">
+      <c r="AZ2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4794,7 +4860,7 @@
           </r>
         </is>
       </c>
-      <c r="AU2" s="3" t="inlineStr">
+      <c r="BA2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6923,6 +6989,36 @@
       </c>
       <c r="W3" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -6953,7 +7049,7 @@
           </r>
         </is>
       </c>
-      <c r="X3" s="3" t="inlineStr">
+      <c r="AD3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6986,7 +7082,7 @@
           </r>
         </is>
       </c>
-      <c r="Y3" s="3" t="inlineStr">
+      <c r="AE3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7004,7 +7100,7 @@
           </r>
         </is>
       </c>
-      <c r="Z3" s="3" t="inlineStr">
+      <c r="AF3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7093,7 +7189,7 @@
           </r>
         </is>
       </c>
-      <c r="AA3" s="3" t="inlineStr">
+      <c r="AG3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7201,7 +7297,7 @@
           </r>
         </is>
       </c>
-      <c r="AB3" s="3" t="inlineStr">
+      <c r="AH3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7243,7 +7339,7 @@
           </r>
         </is>
       </c>
-      <c r="AC3" s="3" t="inlineStr">
+      <c r="AI3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7285,7 +7381,7 @@
           </r>
         </is>
       </c>
-      <c r="AD3" s="3" t="inlineStr">
+      <c r="AJ3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7327,7 +7423,7 @@
           </r>
         </is>
       </c>
-      <c r="AE3" s="3" t="inlineStr">
+      <c r="AK3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7369,7 +7465,7 @@
           </r>
         </is>
       </c>
-      <c r="AF3" s="3" t="inlineStr">
+      <c r="AL3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7411,7 +7507,7 @@
           </r>
         </is>
       </c>
-      <c r="AG3" s="3" t="inlineStr">
+      <c r="AM3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7447,7 +7543,7 @@
           </r>
         </is>
       </c>
-      <c r="AH3" s="3" t="inlineStr">
+      <c r="AN3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7483,7 +7579,7 @@
           </r>
         </is>
       </c>
-      <c r="AI3" s="3" t="inlineStr">
+      <c r="AO3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7526,7 +7622,7 @@
           </r>
         </is>
       </c>
-      <c r="AJ3" s="3" t="inlineStr">
+      <c r="AP3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7569,38 +7665,38 @@
           </r>
         </is>
       </c>
-      <c r="AK3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AL3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AM3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AO3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AP3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="AQ3" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -7802,7 +7898,7 @@
           </r>
         </is>
       </c>
-      <c r="AR3" s="3" t="inlineStr">
+      <c r="AX3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8024,7 +8120,7 @@
           </r>
         </is>
       </c>
-      <c r="AS3" s="3" t="inlineStr">
+      <c r="AY3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8573,7 +8669,7 @@
           </r>
         </is>
       </c>
-      <c r="AT3" s="3" t="inlineStr">
+      <c r="AZ3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8720,7 +8816,7 @@
           </r>
         </is>
       </c>
-      <c r="AU3" s="3" t="inlineStr">
+      <c r="BA3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9891,6 +9987,36 @@
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -9907,7 +10033,7 @@
           </r>
         </is>
       </c>
-      <c r="X4" s="3" t="inlineStr">
+      <c r="AD4" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10008,36 +10134,6 @@
           </r>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AA4" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AB4" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AC4" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AD4" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="AE4" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -10115,6 +10211,36 @@
       </c>
       <c r="AT4" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AX4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AY4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AZ4" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -10196,7 +10322,7 @@
           </r>
         </is>
       </c>
-      <c r="AU4" s="3" t="inlineStr">
+      <c r="BA4" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11161,6 +11287,36 @@
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -11177,17 +11333,17 @@
           </r>
         </is>
       </c>
-      <c r="X5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Z5" s="3" t="inlineStr">
+      <c r="AD5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11236,7 +11392,7 @@
           </r>
         </is>
       </c>
-      <c r="AA5" s="3" t="inlineStr">
+      <c r="AG5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11304,7 +11460,7 @@
           </r>
         </is>
       </c>
-      <c r="AB5" s="3" t="inlineStr">
+      <c r="AH5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11348,7 +11504,7 @@
           </r>
         </is>
       </c>
-      <c r="AC5" s="3" t="inlineStr">
+      <c r="AI5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11392,7 +11548,7 @@
           </r>
         </is>
       </c>
-      <c r="AD5" s="3" t="inlineStr">
+      <c r="AJ5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11436,7 +11592,7 @@
           </r>
         </is>
       </c>
-      <c r="AE5" s="3" t="inlineStr">
+      <c r="AK5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11480,12 +11636,12 @@
           </r>
         </is>
       </c>
-      <c r="AF5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AG5" s="3" t="inlineStr">
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11522,7 +11678,7 @@
           </r>
         </is>
       </c>
-      <c r="AH5" s="3" t="inlineStr">
+      <c r="AN5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11559,7 +11715,7 @@
           </r>
         </is>
       </c>
-      <c r="AI5" s="3" t="inlineStr">
+      <c r="AO5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11603,7 +11759,7 @@
           </r>
         </is>
       </c>
-      <c r="AJ5" s="3" t="inlineStr">
+      <c r="AP5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11647,36 +11803,6 @@
           </r>
         </is>
       </c>
-      <c r="AK5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AL5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AM5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AO5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AP5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="AQ5" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -11694,6 +11820,36 @@
       </c>
       <c r="AT5" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AX5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AY5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AZ5" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -11755,7 +11911,7 @@
           </r>
         </is>
       </c>
-      <c r="AU5" s="3" t="inlineStr">
+      <c r="BA5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12012,6 +12168,36 @@
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -12021,7 +12207,7 @@
           </r>
         </is>
       </c>
-      <c r="X6" s="3" t="inlineStr">
+      <c r="AD6" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12032,7 +12218,7 @@
           </r>
         </is>
       </c>
-      <c r="Y6" s="3" t="inlineStr">
+      <c r="AE6" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12043,7 +12229,7 @@
           </r>
         </is>
       </c>
-      <c r="Z6" s="3" t="inlineStr">
+      <c r="AF6" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12054,7 +12240,7 @@
           </r>
         </is>
       </c>
-      <c r="AA6" s="3" t="inlineStr">
+      <c r="AG6" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12065,36 +12251,6 @@
           </r>
         </is>
       </c>
-      <c r="AB6" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AC6" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AD6" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AE6" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AF6" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AG6" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="AH6" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -12157,6 +12313,36 @@
       </c>
       <c r="AT6" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AX6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AY6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AZ6" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -12166,7 +12352,7 @@
           </r>
         </is>
       </c>
-      <c r="AU6" s="3" t="inlineStr">
+      <c r="BA6" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>

--- a/_downloads/6389148f3813c4a2cb904a2a4100c2de/data_query_matrix.xlsx
+++ b/_downloads/6389148f3813c4a2cb904a2a4100c2de/data_query_matrix.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA6"/>
+  <dimension ref="A1:BB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -443,42 +443,43 @@
     <col width="50" customWidth="1" min="15" max="15"/>
     <col width="29" customWidth="1" min="16" max="16"/>
     <col width="22" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
-    <col width="50" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
-    <col width="22" customWidth="1" min="22" max="22"/>
-    <col width="17" customWidth="1" min="23" max="23"/>
-    <col width="11" customWidth="1" min="24" max="24"/>
-    <col width="13" customWidth="1" min="25" max="25"/>
-    <col width="21" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
-    <col width="17" customWidth="1" min="28" max="28"/>
-    <col width="19" customWidth="1" min="29" max="29"/>
-    <col width="18" customWidth="1" min="30" max="30"/>
-    <col width="24" customWidth="1" min="31" max="31"/>
-    <col width="50" customWidth="1" min="32" max="32"/>
-    <col width="45" customWidth="1" min="33" max="33"/>
-    <col width="10" customWidth="1" min="34" max="34"/>
-    <col width="13" customWidth="1" min="35" max="35"/>
-    <col width="16" customWidth="1" min="36" max="36"/>
-    <col width="10" customWidth="1" min="37" max="37"/>
-    <col width="11" customWidth="1" min="38" max="38"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="24" customWidth="1" min="19" max="19"/>
+    <col width="50" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="17" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="26" max="26"/>
+    <col width="21" customWidth="1" min="27" max="27"/>
+    <col width="15" customWidth="1" min="28" max="28"/>
+    <col width="17" customWidth="1" min="29" max="29"/>
+    <col width="19" customWidth="1" min="30" max="30"/>
+    <col width="18" customWidth="1" min="31" max="31"/>
+    <col width="24" customWidth="1" min="32" max="32"/>
+    <col width="50" customWidth="1" min="33" max="33"/>
+    <col width="45" customWidth="1" min="34" max="34"/>
+    <col width="10" customWidth="1" min="35" max="35"/>
+    <col width="13" customWidth="1" min="36" max="36"/>
+    <col width="16" customWidth="1" min="37" max="37"/>
+    <col width="10" customWidth="1" min="38" max="38"/>
     <col width="11" customWidth="1" min="39" max="39"/>
-    <col width="13" customWidth="1" min="40" max="40"/>
-    <col width="11" customWidth="1" min="41" max="41"/>
+    <col width="11" customWidth="1" min="40" max="40"/>
+    <col width="13" customWidth="1" min="41" max="41"/>
     <col width="11" customWidth="1" min="42" max="42"/>
     <col width="11" customWidth="1" min="43" max="43"/>
-    <col width="12" customWidth="1" min="44" max="44"/>
-    <col width="8" customWidth="1" min="45" max="45"/>
-    <col width="7" customWidth="1" min="46" max="46"/>
-    <col width="8" customWidth="1" min="47" max="47"/>
+    <col width="11" customWidth="1" min="44" max="44"/>
+    <col width="12" customWidth="1" min="45" max="45"/>
+    <col width="8" customWidth="1" min="46" max="46"/>
+    <col width="7" customWidth="1" min="47" max="47"/>
     <col width="8" customWidth="1" min="48" max="48"/>
-    <col width="41" customWidth="1" min="49" max="49"/>
-    <col width="46" customWidth="1" min="50" max="50"/>
-    <col width="50" customWidth="1" min="51" max="51"/>
-    <col width="38" customWidth="1" min="52" max="52"/>
-    <col width="50" customWidth="1" min="53" max="53"/>
+    <col width="8" customWidth="1" min="49" max="49"/>
+    <col width="41" customWidth="1" min="50" max="50"/>
+    <col width="46" customWidth="1" min="51" max="51"/>
+    <col width="50" customWidth="1" min="52" max="52"/>
+    <col width="38" customWidth="1" min="53" max="53"/>
+    <col width="50" customWidth="1" min="54" max="54"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -569,180 +570,185 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>LineContinuation</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
           <t>TryCatch</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Raise</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Thread</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>SendMessage</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>ReceiveMessage</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>MutexDefinition</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>MutexLock</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>MutexUnlock</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>SemaphoreDefinition</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>SemaphoreWait</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>SemaphoreSignal</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>SingleLineComment</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>MultiLineComment</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Print</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Import</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Constant</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Addition</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Subtraction</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Multiplication</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Division</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Remainder</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Floor</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Rounding</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Increment</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Decrement</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>LeftShift</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>RightShift</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>BitAnd</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>BitOr</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>BitXor</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>BitNot</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>Float4VectorMultiplication</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>Float4VectorDotProduct</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>Float4VectorCrossProduct</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>SetFiltering</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>SetJoin</t>
         </is>
@@ -3225,6 +3231,11 @@
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S2" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -3395,7 +3406,7 @@
           </r>
         </is>
       </c>
-      <c r="S2" s="3" t="inlineStr">
+      <c r="T2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3469,11 +3480,6 @@
           </r>
         </is>
       </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="U2" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -3516,6 +3522,11 @@
       </c>
       <c r="AC2" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AD2" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -3526,7 +3537,7 @@
           </r>
         </is>
       </c>
-      <c r="AD2" s="3" t="inlineStr">
+      <c r="AE2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3559,7 +3570,7 @@
           </r>
         </is>
       </c>
-      <c r="AE2" s="3" t="inlineStr">
+      <c r="AF2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3595,13 +3606,13 @@
           </r>
         </is>
       </c>
-      <c r="AF2" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="AG2" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AH2" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -3683,7 +3694,7 @@
           </r>
         </is>
       </c>
-      <c r="AH2" s="3" t="inlineStr">
+      <c r="AI2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3725,7 +3736,7 @@
           </r>
         </is>
       </c>
-      <c r="AI2" s="3" t="inlineStr">
+      <c r="AJ2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3767,7 +3778,7 @@
           </r>
         </is>
       </c>
-      <c r="AJ2" s="3" t="inlineStr">
+      <c r="AK2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3809,7 +3820,7 @@
           </r>
         </is>
       </c>
-      <c r="AK2" s="3" t="inlineStr">
+      <c r="AL2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3851,7 +3862,7 @@
           </r>
         </is>
       </c>
-      <c r="AL2" s="3" t="inlineStr">
+      <c r="AM2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3893,7 +3904,7 @@
           </r>
         </is>
       </c>
-      <c r="AM2" s="3" t="inlineStr">
+      <c r="AN2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3928,7 +3939,7 @@
           </r>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
+      <c r="AO2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3982,7 +3993,7 @@
           </r>
         </is>
       </c>
-      <c r="AO2" s="3" t="inlineStr">
+      <c r="AP2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4025,7 +4036,7 @@
           </r>
         </is>
       </c>
-      <c r="AP2" s="3" t="inlineStr">
+      <c r="AQ2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4068,11 +4079,6 @@
           </r>
         </is>
       </c>
-      <c r="AQ2" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="AR2" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -4080,6 +4086,11 @@
       </c>
       <c r="AS2" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT2" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -4120,7 +4131,7 @@
           </r>
         </is>
       </c>
-      <c r="AT2" s="3" t="inlineStr">
+      <c r="AU2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4162,7 +4173,7 @@
           </r>
         </is>
       </c>
-      <c r="AU2" s="3" t="inlineStr">
+      <c r="AV2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4204,7 +4215,7 @@
           </r>
         </is>
       </c>
-      <c r="AV2" s="3" t="inlineStr">
+      <c r="AW2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4228,7 +4239,7 @@
           </r>
         </is>
       </c>
-      <c r="AW2" s="3" t="inlineStr">
+      <c r="AX2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4364,7 +4375,7 @@
           </r>
         </is>
       </c>
-      <c r="AX2" s="3" t="inlineStr">
+      <c r="AY2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4521,7 +4532,7 @@
           </r>
         </is>
       </c>
-      <c r="AY2" s="3" t="inlineStr">
+      <c r="AZ2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4772,7 +4783,7 @@
           </r>
         </is>
       </c>
-      <c r="AZ2" s="3" t="inlineStr">
+      <c r="BA2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4860,7 +4871,7 @@
           </r>
         </is>
       </c>
-      <c r="BA2" s="3" t="inlineStr">
+      <c r="BB2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6722,6 +6733,11 @@
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -6878,7 +6894,7 @@
           </r>
         </is>
       </c>
-      <c r="S3" s="3" t="inlineStr">
+      <c r="T3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6972,11 +6988,6 @@
           </r>
         </is>
       </c>
-      <c r="T3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="U3" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -7019,6 +7030,11 @@
       </c>
       <c r="AC3" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -7049,7 +7065,7 @@
           </r>
         </is>
       </c>
-      <c r="AD3" s="3" t="inlineStr">
+      <c r="AE3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7082,7 +7098,7 @@
           </r>
         </is>
       </c>
-      <c r="AE3" s="3" t="inlineStr">
+      <c r="AF3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7100,7 +7116,7 @@
           </r>
         </is>
       </c>
-      <c r="AF3" s="3" t="inlineStr">
+      <c r="AG3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7189,7 +7205,7 @@
           </r>
         </is>
       </c>
-      <c r="AG3" s="3" t="inlineStr">
+      <c r="AH3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7297,7 +7313,7 @@
           </r>
         </is>
       </c>
-      <c r="AH3" s="3" t="inlineStr">
+      <c r="AI3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7339,7 +7355,7 @@
           </r>
         </is>
       </c>
-      <c r="AI3" s="3" t="inlineStr">
+      <c r="AJ3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7381,7 +7397,7 @@
           </r>
         </is>
       </c>
-      <c r="AJ3" s="3" t="inlineStr">
+      <c r="AK3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7423,7 +7439,7 @@
           </r>
         </is>
       </c>
-      <c r="AK3" s="3" t="inlineStr">
+      <c r="AL3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7465,7 +7481,7 @@
           </r>
         </is>
       </c>
-      <c r="AL3" s="3" t="inlineStr">
+      <c r="AM3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7507,7 +7523,7 @@
           </r>
         </is>
       </c>
-      <c r="AM3" s="3" t="inlineStr">
+      <c r="AN3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7543,7 +7559,7 @@
           </r>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
+      <c r="AO3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7579,7 +7595,7 @@
           </r>
         </is>
       </c>
-      <c r="AO3" s="3" t="inlineStr">
+      <c r="AP3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7622,7 +7638,7 @@
           </r>
         </is>
       </c>
-      <c r="AP3" s="3" t="inlineStr">
+      <c r="AQ3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7665,11 +7681,6 @@
           </r>
         </is>
       </c>
-      <c r="AQ3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="AR3" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -7697,6 +7708,11 @@
       </c>
       <c r="AW3" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AX3" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -7898,7 +7914,7 @@
           </r>
         </is>
       </c>
-      <c r="AX3" s="3" t="inlineStr">
+      <c r="AY3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8120,7 +8136,7 @@
           </r>
         </is>
       </c>
-      <c r="AY3" s="3" t="inlineStr">
+      <c r="AZ3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8669,7 +8685,7 @@
           </r>
         </is>
       </c>
-      <c r="AZ3" s="3" t="inlineStr">
+      <c r="BA3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8816,7 +8832,7 @@
           </r>
         </is>
       </c>
-      <c r="BA3" s="3" t="inlineStr">
+      <c r="BB3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9933,6 +9949,11 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -9985,11 +10006,6 @@
           </r>
         </is>
       </c>
-      <c r="W4" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -10017,6 +10033,11 @@
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -10033,7 +10054,7 @@
           </r>
         </is>
       </c>
-      <c r="AD4" s="3" t="inlineStr">
+      <c r="AE4" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10134,11 +10155,6 @@
           </r>
         </is>
       </c>
-      <c r="AE4" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="AF4" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -10241,6 +10257,11 @@
       </c>
       <c r="AZ4" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BA4" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -10322,7 +10343,7 @@
           </r>
         </is>
       </c>
-      <c r="BA4" s="3" t="inlineStr">
+      <c r="BB4" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11317,6 +11338,11 @@
       </c>
       <c r="AC5" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -11333,11 +11359,6 @@
           </r>
         </is>
       </c>
-      <c r="AD5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="AE5" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -11345,6 +11366,11 @@
       </c>
       <c r="AF5" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -11392,7 +11418,7 @@
           </r>
         </is>
       </c>
-      <c r="AG5" s="3" t="inlineStr">
+      <c r="AH5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11460,7 +11486,7 @@
           </r>
         </is>
       </c>
-      <c r="AH5" s="3" t="inlineStr">
+      <c r="AI5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11504,7 +11530,7 @@
           </r>
         </is>
       </c>
-      <c r="AI5" s="3" t="inlineStr">
+      <c r="AJ5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11548,7 +11574,7 @@
           </r>
         </is>
       </c>
-      <c r="AJ5" s="3" t="inlineStr">
+      <c r="AK5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11592,7 +11618,7 @@
           </r>
         </is>
       </c>
-      <c r="AK5" s="3" t="inlineStr">
+      <c r="AL5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11636,13 +11662,13 @@
           </r>
         </is>
       </c>
-      <c r="AL5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="AM5" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -11678,7 +11704,7 @@
           </r>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
+      <c r="AO5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11715,7 +11741,7 @@
           </r>
         </is>
       </c>
-      <c r="AO5" s="3" t="inlineStr">
+      <c r="AP5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11759,7 +11785,7 @@
           </r>
         </is>
       </c>
-      <c r="AP5" s="3" t="inlineStr">
+      <c r="AQ5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11803,11 +11829,6 @@
           </r>
         </is>
       </c>
-      <c r="AQ5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="AR5" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -11850,6 +11871,11 @@
       </c>
       <c r="AZ5" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BA5" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -11911,7 +11937,7 @@
           </r>
         </is>
       </c>
-      <c r="BA5" s="3" t="inlineStr">
+      <c r="BB5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12198,6 +12224,11 @@
       </c>
       <c r="AC6" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -12207,7 +12238,7 @@
           </r>
         </is>
       </c>
-      <c r="AD6" s="3" t="inlineStr">
+      <c r="AE6" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12218,7 +12249,7 @@
           </r>
         </is>
       </c>
-      <c r="AE6" s="3" t="inlineStr">
+      <c r="AF6" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12229,7 +12260,7 @@
           </r>
         </is>
       </c>
-      <c r="AF6" s="3" t="inlineStr">
+      <c r="AG6" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12240,7 +12271,7 @@
           </r>
         </is>
       </c>
-      <c r="AG6" s="3" t="inlineStr">
+      <c r="AH6" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12251,11 +12282,6 @@
           </r>
         </is>
       </c>
-      <c r="AH6" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="AI6" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -12343,6 +12369,11 @@
       </c>
       <c r="AZ6" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BA6" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -12352,7 +12383,7 @@
           </r>
         </is>
       </c>
-      <c r="BA6" s="3" t="inlineStr">
+      <c r="BB6" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>

--- a/_downloads/6389148f3813c4a2cb904a2a4100c2de/data_query_matrix.xlsx
+++ b/_downloads/6389148f3813c4a2cb904a2a4100c2de/data_query_matrix.xlsx
@@ -423,63 +423,69 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB6"/>
+  <dimension ref="A1:BH6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="50" customWidth="1" min="12" max="12"/>
-    <col width="37" customWidth="1" min="13" max="13"/>
-    <col width="50" customWidth="1" min="14" max="14"/>
-    <col width="50" customWidth="1" min="15" max="15"/>
-    <col width="29" customWidth="1" min="16" max="16"/>
-    <col width="22" customWidth="1" min="17" max="17"/>
-    <col width="18" customWidth="1" min="18" max="18"/>
-    <col width="24" customWidth="1" min="19" max="19"/>
+    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="31" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="29" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="38" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="50" customWidth="1" min="18" max="18"/>
+    <col width="37" customWidth="1" min="19" max="19"/>
     <col width="50" customWidth="1" min="20" max="20"/>
-    <col width="8" customWidth="1" min="21" max="21"/>
-    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="50" customWidth="1" min="21" max="21"/>
+    <col width="29" customWidth="1" min="22" max="22"/>
     <col width="22" customWidth="1" min="23" max="23"/>
-    <col width="17" customWidth="1" min="24" max="24"/>
-    <col width="11" customWidth="1" min="25" max="25"/>
-    <col width="13" customWidth="1" min="26" max="26"/>
-    <col width="21" customWidth="1" min="27" max="27"/>
-    <col width="15" customWidth="1" min="28" max="28"/>
-    <col width="17" customWidth="1" min="29" max="29"/>
-    <col width="19" customWidth="1" min="30" max="30"/>
-    <col width="18" customWidth="1" min="31" max="31"/>
-    <col width="24" customWidth="1" min="32" max="32"/>
-    <col width="50" customWidth="1" min="33" max="33"/>
-    <col width="45" customWidth="1" min="34" max="34"/>
-    <col width="10" customWidth="1" min="35" max="35"/>
-    <col width="13" customWidth="1" min="36" max="36"/>
-    <col width="16" customWidth="1" min="37" max="37"/>
-    <col width="10" customWidth="1" min="38" max="38"/>
-    <col width="11" customWidth="1" min="39" max="39"/>
-    <col width="11" customWidth="1" min="40" max="40"/>
-    <col width="13" customWidth="1" min="41" max="41"/>
-    <col width="11" customWidth="1" min="42" max="42"/>
-    <col width="11" customWidth="1" min="43" max="43"/>
-    <col width="11" customWidth="1" min="44" max="44"/>
-    <col width="12" customWidth="1" min="45" max="45"/>
-    <col width="8" customWidth="1" min="46" max="46"/>
-    <col width="7" customWidth="1" min="47" max="47"/>
-    <col width="8" customWidth="1" min="48" max="48"/>
-    <col width="8" customWidth="1" min="49" max="49"/>
-    <col width="41" customWidth="1" min="50" max="50"/>
-    <col width="46" customWidth="1" min="51" max="51"/>
-    <col width="50" customWidth="1" min="52" max="52"/>
-    <col width="38" customWidth="1" min="53" max="53"/>
-    <col width="50" customWidth="1" min="54" max="54"/>
+    <col width="18" customWidth="1" min="24" max="24"/>
+    <col width="24" customWidth="1" min="25" max="25"/>
+    <col width="50" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="22" customWidth="1" min="29" max="29"/>
+    <col width="17" customWidth="1" min="30" max="30"/>
+    <col width="11" customWidth="1" min="31" max="31"/>
+    <col width="13" customWidth="1" min="32" max="32"/>
+    <col width="21" customWidth="1" min="33" max="33"/>
+    <col width="15" customWidth="1" min="34" max="34"/>
+    <col width="17" customWidth="1" min="35" max="35"/>
+    <col width="19" customWidth="1" min="36" max="36"/>
+    <col width="18" customWidth="1" min="37" max="37"/>
+    <col width="24" customWidth="1" min="38" max="38"/>
+    <col width="50" customWidth="1" min="39" max="39"/>
+    <col width="45" customWidth="1" min="40" max="40"/>
+    <col width="10" customWidth="1" min="41" max="41"/>
+    <col width="13" customWidth="1" min="42" max="42"/>
+    <col width="16" customWidth="1" min="43" max="43"/>
+    <col width="10" customWidth="1" min="44" max="44"/>
+    <col width="11" customWidth="1" min="45" max="45"/>
+    <col width="11" customWidth="1" min="46" max="46"/>
+    <col width="13" customWidth="1" min="47" max="47"/>
+    <col width="11" customWidth="1" min="48" max="48"/>
+    <col width="11" customWidth="1" min="49" max="49"/>
+    <col width="11" customWidth="1" min="50" max="50"/>
+    <col width="12" customWidth="1" min="51" max="51"/>
+    <col width="8" customWidth="1" min="52" max="52"/>
+    <col width="7" customWidth="1" min="53" max="53"/>
+    <col width="8" customWidth="1" min="54" max="54"/>
+    <col width="8" customWidth="1" min="55" max="55"/>
+    <col width="41" customWidth="1" min="56" max="56"/>
+    <col width="46" customWidth="1" min="57" max="57"/>
+    <col width="50" customWidth="1" min="58" max="58"/>
+    <col width="38" customWidth="1" min="59" max="59"/>
+    <col width="50" customWidth="1" min="60" max="60"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -495,260 +501,290 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>ToCharDate</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>ToCharDateTimezone</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>ToCharNumberThousandSeparator</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>ToCharNumberNegativeBrackets</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ToCharNumberFixedDecimals</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ToDate</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>ForEach</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>CollectionDefinition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>AssociativeArrayDefinition</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Equal</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>NotEqual</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>GreaterThan</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>LogicalAnd</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>LogicalOr</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>LogicalXor</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>ProcedureDefinition</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>FunctionDefinition</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>IfElse</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>SwitchCase</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Loop</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>ForLoop</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>LineContinuation</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>TryCatch</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Raise</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Thread</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>SendMessage</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>ReceiveMessage</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>MutexDefinition</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>MutexLock</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>MutexUnlock</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>SemaphoreDefinition</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>SemaphoreWait</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>SemaphoreSignal</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>SingleLineComment</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>MultiLineComment</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Print</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Import</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Constant</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Addition</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Subtraction</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Multiplication</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>Division</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>Remainder</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>Floor</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>Rounding</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>Increment</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>Decrement</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>LeftShift</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>RightShift</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>BitAnd</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>BitOr</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>BitXor</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>BitNot</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>Float4VectorMultiplication</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>Float4VectorDotProduct</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>Float4VectorCrossProduct</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>SetFiltering</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>SetJoin</t>
         </is>
@@ -847,6 +883,351 @@
           <r>
             <rPr>
               <rFont val="Consolas"/>
+            </rPr>
+            <t>FORMAT</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>date_col</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>'dd.MM.yyyy'</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>FORMAT</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>datetime_col</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>'yyyy-MM-dd HH:mm:ss K'</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>FORMAT</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>num</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>'#,0'</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>FORMAT</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>num</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>'#,0;(#,0)'</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>FORMAT</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>num</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>'N2'</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>CONVERT</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>DATE</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>'31.12.2023'</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>104</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
               <color rgb="00007020"/>
             </rPr>
             <t>DECLARE</t>
@@ -1278,7 +1659,7 @@
           </r>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1523,7 +1904,7 @@
           </r>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1824,7 +2205,7 @@
           </r>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1866,7 +2247,7 @@
           </r>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1915,7 +2296,7 @@
           </r>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1957,22 +2338,22 @@
           </r>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q2" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2145,7 +2526,7 @@
           </r>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="S2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2398,7 +2779,7 @@
           </r>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="T2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2585,7 +2966,7 @@
           </r>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
+      <c r="U2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2769,7 +3150,7 @@
           </r>
         </is>
       </c>
-      <c r="P2" s="3" t="inlineStr">
+      <c r="V2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2950,7 +3331,7 @@
           </r>
         </is>
       </c>
-      <c r="Q2" s="3" t="inlineStr">
+      <c r="W2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3229,12 +3610,12 @@
           </r>
         </is>
       </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
+      <c r="X2" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Y2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3406,7 +3787,7 @@
           </r>
         </is>
       </c>
-      <c r="T2" s="3" t="inlineStr">
+      <c r="Z2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3480,36 +3861,6 @@
           </r>
         </is>
       </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X2" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Z2" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="AA2" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -3527,6 +3878,36 @@
       </c>
       <c r="AD2" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AE2" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AF2" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AG2" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AH2" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AI2" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AJ2" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -3537,7 +3918,7 @@
           </r>
         </is>
       </c>
-      <c r="AE2" s="3" t="inlineStr">
+      <c r="AK2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3570,7 +3951,7 @@
           </r>
         </is>
       </c>
-      <c r="AF2" s="3" t="inlineStr">
+      <c r="AL2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3606,12 +3987,12 @@
           </r>
         </is>
       </c>
-      <c r="AG2" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AH2" s="3" t="inlineStr">
+      <c r="AM2" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AN2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3694,7 +4075,7 @@
           </r>
         </is>
       </c>
-      <c r="AI2" s="3" t="inlineStr">
+      <c r="AO2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3736,7 +4117,7 @@
           </r>
         </is>
       </c>
-      <c r="AJ2" s="3" t="inlineStr">
+      <c r="AP2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3778,7 +4159,7 @@
           </r>
         </is>
       </c>
-      <c r="AK2" s="3" t="inlineStr">
+      <c r="AQ2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3820,7 +4201,7 @@
           </r>
         </is>
       </c>
-      <c r="AL2" s="3" t="inlineStr">
+      <c r="AR2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3862,7 +4243,7 @@
           </r>
         </is>
       </c>
-      <c r="AM2" s="3" t="inlineStr">
+      <c r="AS2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3904,7 +4285,7 @@
           </r>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
+      <c r="AT2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3939,7 +4320,7 @@
           </r>
         </is>
       </c>
-      <c r="AO2" s="3" t="inlineStr">
+      <c r="AU2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3993,7 +4374,7 @@
           </r>
         </is>
       </c>
-      <c r="AP2" s="3" t="inlineStr">
+      <c r="AV2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4036,7 +4417,7 @@
           </r>
         </is>
       </c>
-      <c r="AQ2" s="3" t="inlineStr">
+      <c r="AW2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4079,17 +4460,17 @@
           </r>
         </is>
       </c>
-      <c r="AR2" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AS2" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AT2" s="3" t="inlineStr">
+      <c r="AX2" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AY2" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AZ2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4131,7 +4512,7 @@
           </r>
         </is>
       </c>
-      <c r="AU2" s="3" t="inlineStr">
+      <c r="BA2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4173,7 +4554,7 @@
           </r>
         </is>
       </c>
-      <c r="AV2" s="3" t="inlineStr">
+      <c r="BB2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4215,7 +4596,7 @@
           </r>
         </is>
       </c>
-      <c r="AW2" s="3" t="inlineStr">
+      <c r="BC2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4239,7 +4620,7 @@
           </r>
         </is>
       </c>
-      <c r="AX2" s="3" t="inlineStr">
+      <c r="BD2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4375,7 +4756,7 @@
           </r>
         </is>
       </c>
-      <c r="AY2" s="3" t="inlineStr">
+      <c r="BE2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4532,7 +4913,7 @@
           </r>
         </is>
       </c>
-      <c r="AZ2" s="3" t="inlineStr">
+      <c r="BF2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4783,7 +5164,7 @@
           </r>
         </is>
       </c>
-      <c r="BA2" s="3" t="inlineStr">
+      <c r="BG2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4871,7 +5252,7 @@
           </r>
         </is>
       </c>
-      <c r="BB2" s="3" t="inlineStr">
+      <c r="BH2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5107,6 +5488,416 @@
           <r>
             <rPr>
               <rFont val="Consolas"/>
+              <color rgb="0006287e"/>
+            </rPr>
+            <t>format-date</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00bb60d5"/>
+            </rPr>
+            <t>$</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>date</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>'[D,2].[M,2].[Y,4]'</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0006287e"/>
+            </rPr>
+            <t>format-dateTime</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00bb60d5"/>
+            </rPr>
+            <t>$</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>dt</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>'[Y]-[M,2]-[D,2] [H,2]:[m,2]:[s,2] [z]'</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0006287e"/>
+            </rPr>
+            <t>format-number</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00bb60d5"/>
+            </rPr>
+            <t>$</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>num</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>'#,##0'</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0006287e"/>
+            </rPr>
+            <t>format-number</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00bb60d5"/>
+            </rPr>
+            <t>$</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>num</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>'#,##0;(#,##0)'</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0006287e"/>
+            </rPr>
+            <t>format-number</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00bb60d5"/>
+            </rPr>
+            <t>$</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>num</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>'0.00'</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0006287e"/>
+            </rPr>
+            <t>xs:date</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0006287e"/>
+            </rPr>
+            <t>replace</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00bb60d5"/>
+            </rPr>
+            <t>$</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>str</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>'(\d{2})\.(\d{2})\.(\d{4})'</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>'$3-$2-$1'</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
               <color rgb="00007020"/>
             </rPr>
             <t>for</t>
@@ -5204,7 +5995,7 @@
           </r>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5317,7 +6108,7 @@
           </r>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5474,7 +6265,7 @@
           </r>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5530,7 +6321,7 @@
           </r>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5586,7 +6377,7 @@
           </r>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5642,22 +6433,22 @@
           </r>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5892,7 +6683,7 @@
           </r>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="S3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6162,7 +6953,7 @@
           </r>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="T3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6289,7 +7080,7 @@
           </r>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="U3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6482,7 +7273,7 @@
           </r>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr">
+      <c r="V3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6609,7 +7400,7 @@
           </r>
         </is>
       </c>
-      <c r="Q3" s="3" t="inlineStr">
+      <c r="W3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6731,12 +7522,12 @@
           </r>
         </is>
       </c>
-      <c r="R3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S3" s="3" t="inlineStr">
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6894,7 +7685,7 @@
           </r>
         </is>
       </c>
-      <c r="T3" s="3" t="inlineStr">
+      <c r="Z3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6988,36 +7779,6 @@
           </r>
         </is>
       </c>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Z3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="AA3" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -7035,6 +7796,36 @@
       </c>
       <c r="AD3" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AG3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AI3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -7065,7 +7856,7 @@
           </r>
         </is>
       </c>
-      <c r="AE3" s="3" t="inlineStr">
+      <c r="AK3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7098,7 +7889,7 @@
           </r>
         </is>
       </c>
-      <c r="AF3" s="3" t="inlineStr">
+      <c r="AL3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7116,7 +7907,7 @@
           </r>
         </is>
       </c>
-      <c r="AG3" s="3" t="inlineStr">
+      <c r="AM3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7205,7 +7996,7 @@
           </r>
         </is>
       </c>
-      <c r="AH3" s="3" t="inlineStr">
+      <c r="AN3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7313,7 +8104,7 @@
           </r>
         </is>
       </c>
-      <c r="AI3" s="3" t="inlineStr">
+      <c r="AO3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7355,7 +8146,7 @@
           </r>
         </is>
       </c>
-      <c r="AJ3" s="3" t="inlineStr">
+      <c r="AP3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7397,7 +8188,7 @@
           </r>
         </is>
       </c>
-      <c r="AK3" s="3" t="inlineStr">
+      <c r="AQ3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7439,7 +8230,7 @@
           </r>
         </is>
       </c>
-      <c r="AL3" s="3" t="inlineStr">
+      <c r="AR3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7481,7 +8272,7 @@
           </r>
         </is>
       </c>
-      <c r="AM3" s="3" t="inlineStr">
+      <c r="AS3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7523,7 +8314,7 @@
           </r>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
+      <c r="AT3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7559,7 +8350,7 @@
           </r>
         </is>
       </c>
-      <c r="AO3" s="3" t="inlineStr">
+      <c r="AU3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7595,7 +8386,7 @@
           </r>
         </is>
       </c>
-      <c r="AP3" s="3" t="inlineStr">
+      <c r="AV3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7638,7 +8429,7 @@
           </r>
         </is>
       </c>
-      <c r="AQ3" s="3" t="inlineStr">
+      <c r="AW3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7681,38 +8472,38 @@
           </r>
         </is>
       </c>
-      <c r="AR3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AS3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AT3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AU3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AV3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AW3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="AX3" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AY3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AZ3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BA3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BB3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BC3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BD3" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -7914,7 +8705,7 @@
           </r>
         </is>
       </c>
-      <c r="AY3" s="3" t="inlineStr">
+      <c r="BE3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8136,7 +8927,7 @@
           </r>
         </is>
       </c>
-      <c r="AZ3" s="3" t="inlineStr">
+      <c r="BF3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8685,7 +9476,7 @@
           </r>
         </is>
       </c>
-      <c r="BA3" s="3" t="inlineStr">
+      <c r="BG3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8832,7 +9623,7 @@
           </r>
         </is>
       </c>
-      <c r="BB3" s="3" t="inlineStr">
+      <c r="BH3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9250,6 +10041,36 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -9385,36 +10206,6 @@
           </r>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -9427,6 +10218,36 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -9607,7 +10428,7 @@
           </r>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="T4" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9912,36 +10733,6 @@
           </r>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S4" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -9954,6 +10745,36 @@
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -10006,38 +10827,38 @@
           </r>
         </is>
       </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AA4" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AB4" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AC4" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="AD4" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -10054,7 +10875,7 @@
           </r>
         </is>
       </c>
-      <c r="AE4" s="3" t="inlineStr">
+      <c r="AK4" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10155,36 +10976,6 @@
           </r>
         </is>
       </c>
-      <c r="AF4" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AG4" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AH4" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AI4" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AJ4" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AK4" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="AL4" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -10262,6 +11053,36 @@
       </c>
       <c r="BA4" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BB4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BC4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BD4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BE4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BF4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BG4" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -10343,7 +11164,7 @@
           </r>
         </is>
       </c>
-      <c r="BB4" s="3" t="inlineStr">
+      <c r="BH4" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10527,6 +11348,36 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -10619,12 +11470,12 @@
           </r>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10687,7 +11538,7 @@
           </r>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10750,7 +11601,7 @@
           </r>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10813,32 +11664,32 @@
           </r>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10984,7 +11835,7 @@
           </r>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="U5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11271,36 +12122,6 @@
           </r>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -11343,6 +12164,36 @@
       </c>
       <c r="AD5" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AI5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -11359,17 +12210,17 @@
           </r>
         </is>
       </c>
-      <c r="AE5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AF5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AG5" s="3" t="inlineStr">
+      <c r="AK5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11418,7 +12269,7 @@
           </r>
         </is>
       </c>
-      <c r="AH5" s="3" t="inlineStr">
+      <c r="AN5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11486,7 +12337,7 @@
           </r>
         </is>
       </c>
-      <c r="AI5" s="3" t="inlineStr">
+      <c r="AO5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11530,7 +12381,7 @@
           </r>
         </is>
       </c>
-      <c r="AJ5" s="3" t="inlineStr">
+      <c r="AP5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11574,7 +12425,7 @@
           </r>
         </is>
       </c>
-      <c r="AK5" s="3" t="inlineStr">
+      <c r="AQ5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11618,7 +12469,7 @@
           </r>
         </is>
       </c>
-      <c r="AL5" s="3" t="inlineStr">
+      <c r="AR5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11662,12 +12513,12 @@
           </r>
         </is>
       </c>
-      <c r="AM5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AN5" s="3" t="inlineStr">
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11704,7 +12555,7 @@
           </r>
         </is>
       </c>
-      <c r="AO5" s="3" t="inlineStr">
+      <c r="AU5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11741,7 +12592,7 @@
           </r>
         </is>
       </c>
-      <c r="AP5" s="3" t="inlineStr">
+      <c r="AV5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11785,7 +12636,7 @@
           </r>
         </is>
       </c>
-      <c r="AQ5" s="3" t="inlineStr">
+      <c r="AW5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11829,36 +12680,6 @@
           </r>
         </is>
       </c>
-      <c r="AR5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AS5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AT5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AU5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AV5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AW5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="AX5" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -11876,6 +12697,36 @@
       </c>
       <c r="BA5" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BB5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BC5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BD5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BE5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BF5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BG5" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -11937,7 +12788,7 @@
           </r>
         </is>
       </c>
-      <c r="BB5" s="3" t="inlineStr">
+      <c r="BH5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12052,6 +12903,36 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -12061,7 +12942,7 @@
           </r>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12072,12 +12953,12 @@
           </r>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12088,7 +12969,7 @@
           </r>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12099,38 +12980,38 @@
           </r>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -12140,12 +13021,12 @@
           </r>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr">
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12156,7 +13037,7 @@
           </r>
         </is>
       </c>
-      <c r="Q6" s="3" t="inlineStr">
+      <c r="W6" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12167,36 +13048,6 @@
           </r>
         </is>
       </c>
-      <c r="R6" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S6" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T6" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V6" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W6" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -12229,6 +13080,36 @@
       </c>
       <c r="AD6" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AI6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AJ6" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -12238,7 +13119,7 @@
           </r>
         </is>
       </c>
-      <c r="AE6" s="3" t="inlineStr">
+      <c r="AK6" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12249,7 +13130,7 @@
           </r>
         </is>
       </c>
-      <c r="AF6" s="3" t="inlineStr">
+      <c r="AL6" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12260,7 +13141,7 @@
           </r>
         </is>
       </c>
-      <c r="AG6" s="3" t="inlineStr">
+      <c r="AM6" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12271,7 +13152,7 @@
           </r>
         </is>
       </c>
-      <c r="AH6" s="3" t="inlineStr">
+      <c r="AN6" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12282,36 +13163,6 @@
           </r>
         </is>
       </c>
-      <c r="AI6" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AJ6" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AK6" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AL6" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AM6" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -12374,6 +13225,36 @@
       </c>
       <c r="BA6" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BB6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BC6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BD6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BE6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BF6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BG6" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -12383,7 +13264,7 @@
           </r>
         </is>
       </c>
-      <c r="BB6" s="3" t="inlineStr">
+      <c r="BH6" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>

--- a/_downloads/6389148f3813c4a2cb904a2a4100c2de/data_query_matrix.xlsx
+++ b/_downloads/6389148f3813c4a2cb904a2a4100c2de/data_query_matrix.xlsx
@@ -427,15 +427,15 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="41" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="31" customWidth="1" min="5" max="5"/>
     <col width="38" customWidth="1" min="6" max="6"/>
     <col width="29" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
-    <col width="50" customWidth="1" min="9" max="9"/>
-    <col width="38" customWidth="1" min="10" max="10"/>
+    <col width="37" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
     <col width="50" customWidth="1" min="11" max="11"/>
     <col width="19" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
@@ -444,13 +444,13 @@
     <col width="11" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="50" customWidth="1" min="18" max="18"/>
-    <col width="37" customWidth="1" min="19" max="19"/>
+    <col width="50" customWidth="1" min="19" max="19"/>
     <col width="50" customWidth="1" min="20" max="20"/>
     <col width="50" customWidth="1" min="21" max="21"/>
     <col width="29" customWidth="1" min="22" max="22"/>
-    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="21" customWidth="1" min="23" max="23"/>
     <col width="18" customWidth="1" min="24" max="24"/>
-    <col width="24" customWidth="1" min="25" max="25"/>
+    <col width="23" customWidth="1" min="25" max="25"/>
     <col width="50" customWidth="1" min="26" max="26"/>
     <col width="8" customWidth="1" min="27" max="27"/>
     <col width="13" customWidth="1" min="28" max="28"/>
@@ -463,7 +463,7 @@
     <col width="17" customWidth="1" min="35" max="35"/>
     <col width="19" customWidth="1" min="36" max="36"/>
     <col width="18" customWidth="1" min="37" max="37"/>
-    <col width="24" customWidth="1" min="38" max="38"/>
+    <col width="40" customWidth="1" min="38" max="38"/>
     <col width="50" customWidth="1" min="39" max="39"/>
     <col width="45" customWidth="1" min="40" max="40"/>
     <col width="10" customWidth="1" min="41" max="41"/>
@@ -477,9 +477,9 @@
     <col width="11" customWidth="1" min="49" max="49"/>
     <col width="11" customWidth="1" min="50" max="50"/>
     <col width="12" customWidth="1" min="51" max="51"/>
-    <col width="8" customWidth="1" min="52" max="52"/>
-    <col width="7" customWidth="1" min="53" max="53"/>
-    <col width="8" customWidth="1" min="54" max="54"/>
+    <col width="14" customWidth="1" min="52" max="52"/>
+    <col width="22" customWidth="1" min="53" max="53"/>
+    <col width="26" customWidth="1" min="54" max="54"/>
     <col width="8" customWidth="1" min="55" max="55"/>
     <col width="41" customWidth="1" min="56" max="56"/>
     <col width="46" customWidth="1" min="57" max="57"/>
@@ -809,14 +809,1757 @@
             <rPr>
               <rFont val="Consolas"/>
             </rPr>
-            <t> </t>
+            <t>
+  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>x</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>NUMBER</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>:</t>
           </r>
           <r>
             <rPr>
               <rFont val="Consolas"/>
               <color rgb="00666666"/>
             </rPr>
-            <t>@</t>
+            <t>=</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>42</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>BEGIN</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0060a0b0"/>
+            </rPr>
+            <t xml:space="preserve">-- usage
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>END</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>TO_CHAR</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>date_col</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>'DD.MM.YYYY'</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>TO_CHAR</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>datetime_col</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>'YYYY-MM-DD HH24:MI:SS TZH:TZM'</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>TO_CHAR</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>num</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>'999,999,990'</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>TO_CHAR</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>num</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>'999G990D00PR'</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>TO_CHAR</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>num</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>'999990.00'</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>TO_DATE</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>'31.12.2023'</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>'DD.MM.YYYY'</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>FOR</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>r</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>IN</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>SELECT</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>*</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>FROM</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>table</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>LOOP</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+    </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0060a0b0"/>
+            </rPr>
+            <t xml:space="preserve">-- access r.column
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>END</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>LOOP</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>TYPE</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>NumList</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>IS</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>TABLE</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>OF</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>NUMBER</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>t</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>NumList</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>=</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>NumList</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>2</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>3</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>TYPE</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>Dict</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>IS</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>TABLE</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>OF</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>NUMBER</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>INDEX</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>BY</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>VARCHAR2</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>10</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>t</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>Dict</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>t</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>'a'</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>=</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>t</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>'b'</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>=</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>2</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>=</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>&lt;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q2" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>CREATE</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>OR</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>REPLACE</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>PROCEDURE</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>log_message</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>msg</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>IN</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>VARCHAR2</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>AS</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>BEGIN</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+    </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>DBMS_OUTPUT</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>PUT_LINE</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>msg</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>END</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>CREATE</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>OR</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>REPLACE</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>FUNCTION</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>add</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>NUMBER</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>NUMBER</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>RETURN</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>NUMBER</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>AS</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>BEGIN</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+    </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>RETURN</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>END</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>IF</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
           </r>
           <r>
             <rPr>
@@ -833,21 +2576,423 @@
           <r>
             <rPr>
               <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>INT</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
               <color rgb="00666666"/>
             </rPr>
+            <t>&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>THEN</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+    </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>RETURN</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>ELSE</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+    </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>RETURN</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>END</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>IF</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="U2" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>CASE</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>x</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+    </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>WHEN</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>THEN</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>'one'</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+    </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>WHEN</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>2</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>THEN</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>'two'</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+    </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>ELSE</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>'none'</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>END</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="V2" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>WHILE</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>x</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>LOOP</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+    </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>x</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
             <t>=</t>
           </r>
           <r>
@@ -859,9 +3004,34 @@
           <r>
             <rPr>
               <rFont val="Consolas"/>
+            </rPr>
+            <t>x</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>-</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
               <color rgb="0040a070"/>
             </rPr>
-            <t>42</t>
+            <t>1</t>
           </r>
           <r>
             <rPr>
@@ -876,15 +3046,308 @@
             <t>
 </t>
           </r>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>FORMAT</t>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>END</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>LOOP</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="W2" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>FOR</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>i</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>IN</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>10</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>LOOP</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+    </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0060a0b0"/>
+            </rPr>
+            <t xml:space="preserve">-- body
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>END</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>LOOP</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="X2" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Y2" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>BEGIN</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+    </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>do_something</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>EXCEPTION</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+    </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>WHEN</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>OTHERS</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>THEN</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+        </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>handle_error</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>END</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="Z2" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>RAISE_APPLICATION_ERROR</t>
           </r>
           <r>
             <rPr>
@@ -895,8 +3358,16 @@
           <r>
             <rPr>
               <rFont val="Consolas"/>
-            </rPr>
-            <t>date_col</t>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>-</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>20001</t>
           </r>
           <r>
             <rPr>
@@ -915,2936 +3386,13 @@
               <rFont val="Consolas"/>
               <color rgb="004070a0"/>
             </rPr>
-            <t>'dd.MM.yyyy'</t>
+            <t>'Error'</t>
           </r>
           <r>
             <rPr>
               <rFont val="Consolas"/>
             </rPr>
             <t>)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>FORMAT</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>(</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>datetime_col</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>,</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="004070a0"/>
-            </rPr>
-            <t>'yyyy-MM-dd HH:mm:ss K'</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>FORMAT</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>(</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>num</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>,</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="004070a0"/>
-            </rPr>
-            <t>'#,0'</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>FORMAT</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>(</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>num</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>,</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="004070a0"/>
-            </rPr>
-            <t>'#,0;(#,0)'</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>FORMAT</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>(</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>num</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>,</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="004070a0"/>
-            </rPr>
-            <t>'N2'</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>CONVERT</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>(</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>DATE</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>,</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="004070a0"/>
-            </rPr>
-            <t>'31.12.2023'</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>,</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="0040a070"/>
-            </rPr>
-            <t>104</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>DECLARE</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>cursor_name</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>CURSOR</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>FOR</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>SELECT</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>col</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>FROM</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>table</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>;</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>OPEN</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>cursor_name</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>;</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>FETCH</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>NEXT</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>FROM</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>cursor_name</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>INTO</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t>@</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>item</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>;</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>WHILE</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t>@</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t>@</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>FETCH_STATUS</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t>=</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="0040a070"/>
-            </rPr>
-            <t>0</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>BEGIN</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-    </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="0060a0b0"/>
-            </rPr>
-            <t xml:space="preserve">-- body
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>    </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>FETCH</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>NEXT</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>FROM</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>cursor_name</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>INTO</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t>@</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>item</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>;</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>END</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>DECLARE</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t>@</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>t</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>TABLE</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>(</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>val</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>INT</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>;</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>INSERT</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>INTO</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t>@</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>t</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>VALUES</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>(</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="0040a070"/>
-            </rPr>
-            <t>1</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>,</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>(</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="0040a070"/>
-            </rPr>
-            <t>2</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>,</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>(</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="0040a070"/>
-            </rPr>
-            <t>3</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>;</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>DECLARE</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t>@</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>t</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>TABLE</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>(</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>key_name</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>NVARCHAR</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>(</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="0040a070"/>
-            </rPr>
-            <t>10</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>,</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>val</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>INT</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>;</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>INSERT</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>INTO</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t>@</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>t</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>VALUES</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>(</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="004070a0"/>
-            </rPr>
-            <t>'a'</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>,</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="0040a070"/>
-            </rPr>
-            <t>1</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>,</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>(</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="004070a0"/>
-            </rPr>
-            <t>'b'</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>,</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="0040a070"/>
-            </rPr>
-            <t>2</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>;</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>a</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t>=</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>b</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>a</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t>&lt;</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t>&gt;</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>b</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>a</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t>&gt;</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>b</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-        </is>
-      </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>CREATE</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>PROCEDURE</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>log_message</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t>@</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>msg</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>NVARCHAR</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>(</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>MAX</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>AS</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>BEGIN</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-    </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>PRINT</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t>@</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>msg</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>;</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>END</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>CREATE</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>FUNCTION</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>add</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>(</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t>@</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>a</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>INT</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>,</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t>@</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>b</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>INT</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>RETURNS</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>INT</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>AS</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>BEGIN</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-    </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>RETURN</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t>@</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>a</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t>+</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t>@</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>b</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>END</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>IF</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t>@</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>x</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t>&gt;</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="0040a070"/>
-            </rPr>
-            <t>0</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>BEGIN</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-    </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>RETURN</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="0040a070"/>
-            </rPr>
-            <t>1</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>END</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>ELSE</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>BEGIN</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-    </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>RETURN</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="0040a070"/>
-            </rPr>
-            <t>0</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>END</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>CASE</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t>@</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>x</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-    </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>WHEN</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="0040a070"/>
-            </rPr>
-            <t>1</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>THEN</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="004070a0"/>
-            </rPr>
-            <t>'one'</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-    </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>WHEN</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="0040a070"/>
-            </rPr>
-            <t>2</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>THEN</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="004070a0"/>
-            </rPr>
-            <t>'two'</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-    </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>ELSE</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="004070a0"/>
-            </rPr>
-            <t>'none'</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>END</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>WHILE</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t>@</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>x</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t>&gt;</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="0040a070"/>
-            </rPr>
-            <t>0</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>BEGIN</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-    </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>SET</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t>@</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>x</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t>=</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t>@</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>x</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t>-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="0040a070"/>
-            </rPr>
-            <t>1</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>END</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>DECLARE</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t>@</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>i</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>INT</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t>=</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="0040a070"/>
-            </rPr>
-            <t>0</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>;</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>WHILE</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t>@</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>i</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t>&lt;</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="0040a070"/>
-            </rPr>
-            <t>10</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>BEGIN</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-    </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="0060a0b0"/>
-            </rPr>
-            <t xml:space="preserve">-- body
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>    </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>SET</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t>@</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>i</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t>=</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t>@</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>i</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t>+</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="0040a070"/>
-            </rPr>
-            <t>1</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>;</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>END</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-        </is>
-      </c>
-      <c r="X2" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>BEGIN</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>TRY</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-    </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>EXEC</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>do_something</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>;</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>END</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>TRY</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>BEGIN</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>CATCH</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-    </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>EXEC</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>handle_error</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>;</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>END</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>CATCH</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-        </is>
-      </c>
-      <c r="Z2" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>THROW</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="0040a070"/>
-            </rPr>
-            <t>50000</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>,</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="004070a0"/>
-            </rPr>
-            <t>'Error'</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>,</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="0040a070"/>
-            </rPr>
-            <t>1</t>
           </r>
           <r>
             <rPr>
@@ -3957,13 +3505,25 @@
             <rPr>
               <rFont val="Consolas"/>
             </rPr>
-            <t>PRINT</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
+            <t>DBMS_OUTPUT</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>PUT_LINE</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
           </r>
           <r>
             <rPr>
@@ -3976,6 +3536,12 @@
             <rPr>
               <rFont val="Consolas"/>
             </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
             <t>;</t>
           </r>
           <r>
@@ -3997,42 +3563,88 @@
           <r>
             <rPr>
               <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>DECLARE</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
+            </rPr>
+            <t>MAX_VAL</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>CONSTANT</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>NUMBER</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>:</t>
           </r>
           <r>
             <rPr>
               <rFont val="Consolas"/>
               <color rgb="00666666"/>
             </rPr>
-            <t>@</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>MAX</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00007020"/>
-            </rPr>
-            <t>INT</t>
+            <t>=</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>100</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="AO2" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
           </r>
           <r>
             <rPr>
@@ -4045,7 +3657,269 @@
               <rFont val="Consolas"/>
               <color rgb="00666666"/>
             </rPr>
-            <t>=</t>
+            <t>+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="AP2" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>-</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="AQ2" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>*</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="AR2" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>/</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="AS2" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>MOD</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="AT2" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>FLOOR</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="AU2" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>ROUND</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
           </r>
           <r>
             <rPr>
@@ -4058,24 +3932,24 @@
               <rFont val="Consolas"/>
               <color rgb="0040a070"/>
             </rPr>
-            <t>100</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>;</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-        </is>
-      </c>
-      <c r="AO2" s="3" t="inlineStr">
+            <t>0</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="AV2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4105,6 +3979,107 @@
           <r>
             <rPr>
               <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="AW2" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>-</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="AX2" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AY2" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AZ2" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>BITAND</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
             </rPr>
             <t>b</t>
           </r>
@@ -4112,12 +4087,18 @@
             <rPr>
               <rFont val="Consolas"/>
             </rPr>
-            <t>
-</t>
-          </r>
-        </is>
-      </c>
-      <c r="AP2" s="3" t="inlineStr">
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="BA2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4136,6 +4117,31 @@
               <rFont val="Consolas"/>
               <color rgb="00666666"/>
             </rPr>
+            <t>+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
             <t>-</t>
           </r>
           <r>
@@ -4148,18 +4154,54 @@
             <rPr>
               <rFont val="Consolas"/>
             </rPr>
+            <t>BITAND</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
             <t>b</t>
           </r>
           <r>
             <rPr>
               <rFont val="Consolas"/>
             </rPr>
-            <t>
-</t>
-          </r>
-        </is>
-      </c>
-      <c r="AQ2" s="3" t="inlineStr">
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="BB2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4178,6 +4220,57 @@
               <rFont val="Consolas"/>
               <color rgb="00666666"/>
             </rPr>
+            <t>+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>-</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>2</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
             <t>*</t>
           </r>
           <r>
@@ -4190,125 +4283,42 @@
             <rPr>
               <rFont val="Consolas"/>
             </rPr>
+            <t>BITAND</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
             <t>b</t>
           </r>
           <r>
             <rPr>
               <rFont val="Consolas"/>
             </rPr>
-            <t>
-</t>
-          </r>
-        </is>
-      </c>
-      <c r="AR2" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>a</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t>/</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>b</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-        </is>
-      </c>
-      <c r="AS2" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>a</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t>%</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>b</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-        </is>
-      </c>
-      <c r="AT2" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>FLOOR</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>(</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>a</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
             <t>)</t>
           </r>
           <r>
@@ -4320,304 +4330,9 @@
           </r>
         </is>
       </c>
-      <c r="AU2" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>ROUND</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>(</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>a</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>,</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="0040a070"/>
-            </rPr>
-            <t>0</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-        </is>
-      </c>
-      <c r="AV2" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>a</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t>+</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="0040a070"/>
-            </rPr>
-            <t>1</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-        </is>
-      </c>
-      <c r="AW2" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>a</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t>-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="0040a070"/>
-            </rPr>
-            <t>1</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-        </is>
-      </c>
-      <c r="AX2" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AY2" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AZ2" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>a</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t>&amp;</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>b</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-        </is>
-      </c>
-      <c r="BA2" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>a</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t>|</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>b</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-        </is>
-      </c>
-      <c r="BB2" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>a</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t>^</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>b</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-        </is>
-      </c>
       <c r="BC2" s="3" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t>~</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>a</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-            </rPr>
-            <t>
-</t>
-          </r>
+          <t>N/A</t>
         </is>
       </c>
       <c r="BD2" s="3" t="inlineStr">

--- a/_downloads/6389148f3813c4a2cb904a2a4100c2de/data_query_matrix.xlsx
+++ b/_downloads/6389148f3813c4a2cb904a2a4100c2de/data_query_matrix.xlsx
@@ -423,69 +423,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH6"/>
+  <dimension ref="A1:BJ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="31" customWidth="1" min="5" max="5"/>
-    <col width="38" customWidth="1" min="6" max="6"/>
-    <col width="29" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
-    <col width="37" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
-    <col width="50" customWidth="1" min="11" max="11"/>
-    <col width="19" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="17" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="41" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="31" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
+    <col width="29" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="37" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
+    <col width="50" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="50" customWidth="1" min="18" max="18"/>
-    <col width="50" customWidth="1" min="19" max="19"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
     <col width="50" customWidth="1" min="20" max="20"/>
     <col width="50" customWidth="1" min="21" max="21"/>
-    <col width="29" customWidth="1" min="22" max="22"/>
-    <col width="21" customWidth="1" min="23" max="23"/>
-    <col width="18" customWidth="1" min="24" max="24"/>
-    <col width="23" customWidth="1" min="25" max="25"/>
-    <col width="50" customWidth="1" min="26" max="26"/>
-    <col width="8" customWidth="1" min="27" max="27"/>
-    <col width="13" customWidth="1" min="28" max="28"/>
-    <col width="22" customWidth="1" min="29" max="29"/>
-    <col width="17" customWidth="1" min="30" max="30"/>
-    <col width="11" customWidth="1" min="31" max="31"/>
-    <col width="13" customWidth="1" min="32" max="32"/>
-    <col width="21" customWidth="1" min="33" max="33"/>
-    <col width="15" customWidth="1" min="34" max="34"/>
-    <col width="17" customWidth="1" min="35" max="35"/>
-    <col width="19" customWidth="1" min="36" max="36"/>
-    <col width="18" customWidth="1" min="37" max="37"/>
-    <col width="40" customWidth="1" min="38" max="38"/>
-    <col width="50" customWidth="1" min="39" max="39"/>
-    <col width="45" customWidth="1" min="40" max="40"/>
-    <col width="10" customWidth="1" min="41" max="41"/>
-    <col width="13" customWidth="1" min="42" max="42"/>
-    <col width="16" customWidth="1" min="43" max="43"/>
-    <col width="10" customWidth="1" min="44" max="44"/>
-    <col width="11" customWidth="1" min="45" max="45"/>
-    <col width="11" customWidth="1" min="46" max="46"/>
-    <col width="13" customWidth="1" min="47" max="47"/>
+    <col width="50" customWidth="1" min="22" max="22"/>
+    <col width="50" customWidth="1" min="23" max="23"/>
+    <col width="29" customWidth="1" min="24" max="24"/>
+    <col width="21" customWidth="1" min="25" max="25"/>
+    <col width="18" customWidth="1" min="26" max="26"/>
+    <col width="23" customWidth="1" min="27" max="27"/>
+    <col width="50" customWidth="1" min="28" max="28"/>
+    <col width="8" customWidth="1" min="29" max="29"/>
+    <col width="13" customWidth="1" min="30" max="30"/>
+    <col width="22" customWidth="1" min="31" max="31"/>
+    <col width="17" customWidth="1" min="32" max="32"/>
+    <col width="11" customWidth="1" min="33" max="33"/>
+    <col width="13" customWidth="1" min="34" max="34"/>
+    <col width="21" customWidth="1" min="35" max="35"/>
+    <col width="15" customWidth="1" min="36" max="36"/>
+    <col width="17" customWidth="1" min="37" max="37"/>
+    <col width="19" customWidth="1" min="38" max="38"/>
+    <col width="18" customWidth="1" min="39" max="39"/>
+    <col width="40" customWidth="1" min="40" max="40"/>
+    <col width="50" customWidth="1" min="41" max="41"/>
+    <col width="45" customWidth="1" min="42" max="42"/>
+    <col width="10" customWidth="1" min="43" max="43"/>
+    <col width="13" customWidth="1" min="44" max="44"/>
+    <col width="16" customWidth="1" min="45" max="45"/>
+    <col width="10" customWidth="1" min="46" max="46"/>
+    <col width="11" customWidth="1" min="47" max="47"/>
     <col width="11" customWidth="1" min="48" max="48"/>
-    <col width="11" customWidth="1" min="49" max="49"/>
+    <col width="13" customWidth="1" min="49" max="49"/>
     <col width="11" customWidth="1" min="50" max="50"/>
-    <col width="12" customWidth="1" min="51" max="51"/>
-    <col width="14" customWidth="1" min="52" max="52"/>
-    <col width="22" customWidth="1" min="53" max="53"/>
-    <col width="26" customWidth="1" min="54" max="54"/>
-    <col width="8" customWidth="1" min="55" max="55"/>
-    <col width="41" customWidth="1" min="56" max="56"/>
-    <col width="46" customWidth="1" min="57" max="57"/>
-    <col width="50" customWidth="1" min="58" max="58"/>
-    <col width="38" customWidth="1" min="59" max="59"/>
+    <col width="11" customWidth="1" min="51" max="51"/>
+    <col width="11" customWidth="1" min="52" max="52"/>
+    <col width="12" customWidth="1" min="53" max="53"/>
+    <col width="14" customWidth="1" min="54" max="54"/>
+    <col width="22" customWidth="1" min="55" max="55"/>
+    <col width="26" customWidth="1" min="56" max="56"/>
+    <col width="8" customWidth="1" min="57" max="57"/>
+    <col width="41" customWidth="1" min="58" max="58"/>
+    <col width="46" customWidth="1" min="59" max="59"/>
     <col width="50" customWidth="1" min="60" max="60"/>
+    <col width="38" customWidth="1" min="61" max="61"/>
+    <col width="50" customWidth="1" min="62" max="62"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -501,290 +503,300 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Sort</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Distinct</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>ToCharDate</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>ToCharDateTimezone</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ToCharNumberThousandSeparator</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>ToCharNumberNegativeBrackets</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>ToCharNumberFixedDecimals</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>ToDate</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>ForEach</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>CollectionDefinition</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>AssociativeArrayDefinition</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Equal</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>NotEqual</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>GreaterThan</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>LogicalAnd</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>LogicalOr</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>LogicalXor</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>ProcedureDefinition</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>FunctionDefinition</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>IfElse</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>SwitchCase</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Loop</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>ForLoop</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>LineContinuation</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>TryCatch</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Raise</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Thread</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>SendMessage</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>ReceiveMessage</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>MutexDefinition</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>MutexLock</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>MutexUnlock</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>SemaphoreDefinition</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>SemaphoreWait</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>SemaphoreSignal</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>SingleLineComment</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>MultiLineComment</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Print</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Import</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Constant</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Addition</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>Subtraction</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>Multiplication</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>Division</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>Remainder</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>Floor</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>Rounding</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>Increment</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>Decrement</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>LeftShift</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>RightShift</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>BitAnd</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>BitOr</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>BitXor</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>BitNot</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>Float4VectorMultiplication</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>Float4VectorDotProduct</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Float4VectorCrossProduct</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>SetFiltering</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>SetJoin</t>
         </is>
@@ -925,6 +937,184 @@
           <r>
             <rPr>
               <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>SELECT</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>*</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>FROM</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>table</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>ORDER</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>BY</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>column</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>SELECT</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>DISTINCT</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>column</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>FROM</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>table</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
             </rPr>
             <t>TO_CHAR</t>
           </r>
@@ -974,7 +1164,7 @@
           </r>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1028,7 +1218,7 @@
           </r>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1082,7 +1272,7 @@
           </r>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1136,7 +1326,7 @@
           </r>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1190,7 +1380,7 @@
           </r>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1245,7 +1435,7 @@
           </r>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1404,7 +1594,7 @@
           </r>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1611,7 +1801,7 @@
           </r>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1927,7 +2117,7 @@
           </r>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1969,7 +2159,7 @@
           </r>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2018,7 +2208,7 @@
           </r>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2060,16 +2250,6 @@
           </r>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -2077,6 +2257,16 @@
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -2283,7 +2473,7 @@
           </r>
         </is>
       </c>
-      <c r="S2" s="3" t="inlineStr">
+      <c r="U2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2546,7 +2736,7 @@
           </r>
         </is>
       </c>
-      <c r="T2" s="3" t="inlineStr">
+      <c r="V2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2728,7 +2918,7 @@
           </r>
         </is>
       </c>
-      <c r="U2" s="3" t="inlineStr">
+      <c r="W2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2905,7 +3095,7 @@
           </r>
         </is>
       </c>
-      <c r="V2" s="3" t="inlineStr">
+      <c r="X2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3080,7 +3270,7 @@
           </r>
         </is>
       </c>
-      <c r="W2" s="3" t="inlineStr">
+      <c r="Y2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3207,12 +3397,12 @@
           </r>
         </is>
       </c>
-      <c r="X2" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Y2" s="3" t="inlineStr">
+      <c r="Z2" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AA2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3341,7 +3531,7 @@
           </r>
         </is>
       </c>
-      <c r="Z2" s="3" t="inlineStr">
+      <c r="AB2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3409,16 +3599,6 @@
           </r>
         </is>
       </c>
-      <c r="AA2" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AB2" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="AC2" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -3456,6 +3636,16 @@
       </c>
       <c r="AJ2" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AK2" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AL2" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -3466,7 +3656,7 @@
           </r>
         </is>
       </c>
-      <c r="AK2" s="3" t="inlineStr">
+      <c r="AM2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3499,7 +3689,7 @@
           </r>
         </is>
       </c>
-      <c r="AL2" s="3" t="inlineStr">
+      <c r="AN2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3553,12 +3743,12 @@
           </r>
         </is>
       </c>
-      <c r="AM2" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AN2" s="3" t="inlineStr">
+      <c r="AO2" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AP2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3638,7 +3828,7 @@
           </r>
         </is>
       </c>
-      <c r="AO2" s="3" t="inlineStr">
+      <c r="AQ2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3680,7 +3870,7 @@
           </r>
         </is>
       </c>
-      <c r="AP2" s="3" t="inlineStr">
+      <c r="AR2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3722,7 +3912,7 @@
           </r>
         </is>
       </c>
-      <c r="AQ2" s="3" t="inlineStr">
+      <c r="AS2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3764,7 +3954,7 @@
           </r>
         </is>
       </c>
-      <c r="AR2" s="3" t="inlineStr">
+      <c r="AT2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3806,7 +3996,7 @@
           </r>
         </is>
       </c>
-      <c r="AS2" s="3" t="inlineStr">
+      <c r="AU2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3860,7 +4050,7 @@
           </r>
         </is>
       </c>
-      <c r="AT2" s="3" t="inlineStr">
+      <c r="AV2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3895,7 +4085,7 @@
           </r>
         </is>
       </c>
-      <c r="AU2" s="3" t="inlineStr">
+      <c r="AW2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3949,7 +4139,7 @@
           </r>
         </is>
       </c>
-      <c r="AV2" s="3" t="inlineStr">
+      <c r="AX2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3992,7 +4182,7 @@
           </r>
         </is>
       </c>
-      <c r="AW2" s="3" t="inlineStr">
+      <c r="AY2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4035,18 +4225,18 @@
           </r>
         </is>
       </c>
-      <c r="AX2" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AY2" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="AZ2" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BA2" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BB2" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -4098,7 +4288,7 @@
           </r>
         </is>
       </c>
-      <c r="BA2" s="3" t="inlineStr">
+      <c r="BC2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4201,7 +4391,7 @@
           </r>
         </is>
       </c>
-      <c r="BB2" s="3" t="inlineStr">
+      <c r="BD2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4330,12 +4520,12 @@
           </r>
         </is>
       </c>
-      <c r="BC2" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="BD2" s="3" t="inlineStr">
+      <c r="BE2" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BF2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4471,7 +4661,7 @@
           </r>
         </is>
       </c>
-      <c r="BE2" s="3" t="inlineStr">
+      <c r="BG2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4628,7 +4818,7 @@
           </r>
         </is>
       </c>
-      <c r="BF2" s="3" t="inlineStr">
+      <c r="BH2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4879,7 +5069,7 @@
           </r>
         </is>
       </c>
-      <c r="BG2" s="3" t="inlineStr">
+      <c r="BI2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4967,7 +5157,7 @@
           </r>
         </is>
       </c>
-      <c r="BH2" s="3" t="inlineStr">
+      <c r="BJ2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5203,8 +5393,184 @@
           <r>
             <rPr>
               <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>for</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00bb60d5"/>
+            </rPr>
+            <t>$</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>x</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>in</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00bb60d5"/>
+            </rPr>
+            <t>$</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>col</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>order by</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00bb60d5"/>
+            </rPr>
+            <t>$</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>x</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>return</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00bb60d5"/>
+            </rPr>
+            <t>$</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>x</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
               <color rgb="0006287e"/>
             </rPr>
+            <t>distinct-values</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00bb60d5"/>
+            </rPr>
+            <t>$</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>col</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0006287e"/>
+            </rPr>
             <t>format-date</t>
           </r>
           <r>
@@ -5260,7 +5626,7 @@
           </r>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5322,7 +5688,7 @@
           </r>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5384,7 +5750,7 @@
           </r>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5446,7 +5812,7 @@
           </r>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5508,7 +5874,7 @@
           </r>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5608,7 +5974,7 @@
           </r>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5710,7 +6076,7 @@
           </r>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5823,7 +6189,7 @@
           </r>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5980,7 +6346,7 @@
           </r>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6036,7 +6402,7 @@
           </r>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6092,7 +6458,7 @@
           </r>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6148,16 +6514,6 @@
           </r>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -6165,6 +6521,16 @@
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -6398,7 +6764,7 @@
           </r>
         </is>
       </c>
-      <c r="S3" s="3" t="inlineStr">
+      <c r="U3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6668,7 +7034,7 @@
           </r>
         </is>
       </c>
-      <c r="T3" s="3" t="inlineStr">
+      <c r="V3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6795,7 +7161,7 @@
           </r>
         </is>
       </c>
-      <c r="U3" s="3" t="inlineStr">
+      <c r="W3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6988,7 +7354,7 @@
           </r>
         </is>
       </c>
-      <c r="V3" s="3" t="inlineStr">
+      <c r="X3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7115,7 +7481,7 @@
           </r>
         </is>
       </c>
-      <c r="W3" s="3" t="inlineStr">
+      <c r="Y3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7237,12 +7603,12 @@
           </r>
         </is>
       </c>
-      <c r="X3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Y3" s="3" t="inlineStr">
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7400,7 +7766,7 @@
           </r>
         </is>
       </c>
-      <c r="Z3" s="3" t="inlineStr">
+      <c r="AB3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7494,16 +7860,6 @@
           </r>
         </is>
       </c>
-      <c r="AA3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AB3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="AC3" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -7541,6 +7897,16 @@
       </c>
       <c r="AJ3" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AK3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -7571,7 +7937,7 @@
           </r>
         </is>
       </c>
-      <c r="AK3" s="3" t="inlineStr">
+      <c r="AM3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7604,7 +7970,7 @@
           </r>
         </is>
       </c>
-      <c r="AL3" s="3" t="inlineStr">
+      <c r="AN3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7622,7 +7988,7 @@
           </r>
         </is>
       </c>
-      <c r="AM3" s="3" t="inlineStr">
+      <c r="AO3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7711,7 +8077,7 @@
           </r>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
+      <c r="AP3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7819,7 +8185,7 @@
           </r>
         </is>
       </c>
-      <c r="AO3" s="3" t="inlineStr">
+      <c r="AQ3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7861,7 +8227,7 @@
           </r>
         </is>
       </c>
-      <c r="AP3" s="3" t="inlineStr">
+      <c r="AR3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7903,7 +8269,7 @@
           </r>
         </is>
       </c>
-      <c r="AQ3" s="3" t="inlineStr">
+      <c r="AS3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7945,7 +8311,7 @@
           </r>
         </is>
       </c>
-      <c r="AR3" s="3" t="inlineStr">
+      <c r="AT3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7987,7 +8353,7 @@
           </r>
         </is>
       </c>
-      <c r="AS3" s="3" t="inlineStr">
+      <c r="AU3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8029,7 +8395,7 @@
           </r>
         </is>
       </c>
-      <c r="AT3" s="3" t="inlineStr">
+      <c r="AV3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8065,7 +8431,7 @@
           </r>
         </is>
       </c>
-      <c r="AU3" s="3" t="inlineStr">
+      <c r="AW3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8101,7 +8467,7 @@
           </r>
         </is>
       </c>
-      <c r="AV3" s="3" t="inlineStr">
+      <c r="AX3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8144,7 +8510,7 @@
           </r>
         </is>
       </c>
-      <c r="AW3" s="3" t="inlineStr">
+      <c r="AY3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8187,16 +8553,6 @@
           </r>
         </is>
       </c>
-      <c r="AX3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AY3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="AZ3" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -8219,6 +8575,16 @@
       </c>
       <c r="BD3" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BE3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BF3" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -8420,7 +8786,7 @@
           </r>
         </is>
       </c>
-      <c r="BE3" s="3" t="inlineStr">
+      <c r="BG3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8642,7 +9008,7 @@
           </r>
         </is>
       </c>
-      <c r="BF3" s="3" t="inlineStr">
+      <c r="BH3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9191,7 +9557,7 @@
           </r>
         </is>
       </c>
-      <c r="BG3" s="3" t="inlineStr">
+      <c r="BI3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9338,7 +9704,7 @@
           </r>
         </is>
       </c>
-      <c r="BH3" s="3" t="inlineStr">
+      <c r="BJ3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9751,7 +10117,129 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>query</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>{</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>users</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>orderBy</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0060add5"/>
+            </rPr>
+            <t>NAME_ASC</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>{</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>name</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>}</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>}</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -9786,6 +10274,16 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -9921,16 +10419,6 @@
           </r>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -9963,6 +10451,16 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -10143,7 +10641,7 @@
           </r>
         </is>
       </c>
-      <c r="T4" s="3" t="inlineStr">
+      <c r="V4" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10448,16 +10946,6 @@
           </r>
         </is>
       </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V4" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -10490,6 +10978,16 @@
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -10542,16 +11040,6 @@
           </r>
         </is>
       </c>
-      <c r="AD4" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AE4" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="AF4" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -10574,6 +11062,16 @@
       </c>
       <c r="AJ4" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AK4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -10590,7 +11088,7 @@
           </r>
         </is>
       </c>
-      <c r="AK4" s="3" t="inlineStr">
+      <c r="AM4" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10691,16 +11189,6 @@
           </r>
         </is>
       </c>
-      <c r="AL4" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AM4" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="AN4" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -10798,6 +11286,16 @@
       </c>
       <c r="BG4" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BH4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BI4" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -10879,7 +11377,7 @@
           </r>
         </is>
       </c>
-      <c r="BH4" s="3" t="inlineStr">
+      <c r="BJ4" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11058,12 +11556,265 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>SELECT</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00bb60d5"/>
+            </rPr>
+            <t>?name</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>WHERE</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>{</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00bb60d5"/>
+            </rPr>
+            <t>?u</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>name</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00bb60d5"/>
+            </rPr>
+            <t>?name</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>}</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>ORDER BY</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00bb60d5"/>
+            </rPr>
+            <t>?name</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>SELECT</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>DISTINCT</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00bb60d5"/>
+            </rPr>
+            <t>?name</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>WHERE</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>{</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00bb60d5"/>
+            </rPr>
+            <t>?u</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>name</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00bb60d5"/>
+            </rPr>
+            <t>?name</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>}</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -11093,6 +11844,16 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -11185,12 +11946,12 @@
           </r>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11253,7 +12014,7 @@
           </r>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11316,7 +12077,7 @@
           </r>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11379,16 +12140,6 @@
           </r>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -11406,6 +12157,16 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -11550,7 +12311,7 @@
           </r>
         </is>
       </c>
-      <c r="U5" s="3" t="inlineStr">
+      <c r="W5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11837,16 +12598,6 @@
           </r>
         </is>
       </c>
-      <c r="V5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -11909,6 +12660,16 @@
       </c>
       <c r="AJ5" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AK5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -11925,18 +12686,18 @@
           </r>
         </is>
       </c>
-      <c r="AK5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AL5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="AM5" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -11984,7 +12745,7 @@
           </r>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
+      <c r="AP5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12052,7 +12813,7 @@
           </r>
         </is>
       </c>
-      <c r="AO5" s="3" t="inlineStr">
+      <c r="AQ5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12096,7 +12857,7 @@
           </r>
         </is>
       </c>
-      <c r="AP5" s="3" t="inlineStr">
+      <c r="AR5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12140,7 +12901,7 @@
           </r>
         </is>
       </c>
-      <c r="AQ5" s="3" t="inlineStr">
+      <c r="AS5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12184,7 +12945,7 @@
           </r>
         </is>
       </c>
-      <c r="AR5" s="3" t="inlineStr">
+      <c r="AT5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12228,12 +12989,12 @@
           </r>
         </is>
       </c>
-      <c r="AS5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AT5" s="3" t="inlineStr">
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12270,7 +13031,7 @@
           </r>
         </is>
       </c>
-      <c r="AU5" s="3" t="inlineStr">
+      <c r="AW5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12307,7 +13068,7 @@
           </r>
         </is>
       </c>
-      <c r="AV5" s="3" t="inlineStr">
+      <c r="AX5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12351,7 +13112,7 @@
           </r>
         </is>
       </c>
-      <c r="AW5" s="3" t="inlineStr">
+      <c r="AY5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12395,16 +13156,6 @@
           </r>
         </is>
       </c>
-      <c r="AX5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AY5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="AZ5" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -12442,6 +13193,16 @@
       </c>
       <c r="BG5" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BH5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BI5" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -12503,7 +13264,7 @@
           </r>
         </is>
       </c>
-      <c r="BH5" s="3" t="inlineStr">
+      <c r="BJ5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12648,6 +13409,16 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -12657,7 +13428,7 @@
           </r>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12668,12 +13439,12 @@
           </r>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12684,7 +13455,7 @@
           </r>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="O6" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12695,16 +13466,6 @@
           </r>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -12727,6 +13488,16 @@
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -12736,12 +13507,12 @@
           </r>
         </is>
       </c>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V6" s="3" t="inlineStr">
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12752,7 +13523,7 @@
           </r>
         </is>
       </c>
-      <c r="W6" s="3" t="inlineStr">
+      <c r="Y6" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12763,16 +13534,6 @@
           </r>
         </is>
       </c>
-      <c r="X6" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -12825,6 +13586,16 @@
       </c>
       <c r="AJ6" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AK6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -12834,7 +13605,7 @@
           </r>
         </is>
       </c>
-      <c r="AK6" s="3" t="inlineStr">
+      <c r="AM6" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12845,7 +13616,7 @@
           </r>
         </is>
       </c>
-      <c r="AL6" s="3" t="inlineStr">
+      <c r="AN6" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12856,7 +13627,7 @@
           </r>
         </is>
       </c>
-      <c r="AM6" s="3" t="inlineStr">
+      <c r="AO6" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12867,7 +13638,7 @@
           </r>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
+      <c r="AP6" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12878,16 +13649,6 @@
           </r>
         </is>
       </c>
-      <c r="AO6" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AP6" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="AQ6" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -12970,6 +13731,16 @@
       </c>
       <c r="BG6" s="3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BH6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BI6" s="3" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Consolas"/>
@@ -12979,7 +13750,7 @@
           </r>
         </is>
       </c>
-      <c r="BH6" s="3" t="inlineStr">
+      <c r="BJ6" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
